--- a/data/source/weekly/cs-en-us-019pct.xlsx
+++ b/data/source/weekly/cs-en-us-019pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -895,32 +895,32 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="15">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="14">
+        <v>0</v>
       </c>
       <c r="I15" s="15">
         <v>2</v>
       </c>
       <c r="J15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L15" s="14">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>100</v>
       </c>
       <c r="N15" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -940,37 +940,37 @@
         <v>20</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E16" s="14">
         <v>-100</v>
       </c>
       <c r="F16" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" s="15">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H16" s="14">
-        <v>-33.333333333333</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="I16" s="15">
         <v>9</v>
       </c>
       <c r="J16" s="15">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K16" s="14">
-        <v>-40</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L16" s="14">
         <v>-62.5</v>
       </c>
       <c r="M16" s="14">
-        <v>-47.058823529411</v>
+        <v>-55</v>
       </c>
       <c r="N16" s="14">
-        <v>-93.75</v>
+        <v>-94.339622641509</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D17" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E17" s="14">
-        <v>400</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G17" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H17" s="14">
-        <v>37.5</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I17" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J17" s="15">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K17" s="14">
-        <v>38.461538461538</v>
+        <v>17.647058823529</v>
       </c>
       <c r="L17" s="14">
-        <v>157.142857142857</v>
+        <v>185.714285714286</v>
       </c>
       <c r="M17" s="14">
-        <v>125</v>
+        <v>122.222222222222</v>
       </c>
       <c r="N17" s="14">
-        <v>-14.285714285714</v>
+        <v>-23.076923076923</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E18" s="14">
-        <v>100</v>
+        <v>-87.5</v>
       </c>
       <c r="F18" s="15">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G18" s="15">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H18" s="14">
-        <v>-39.130434782608</v>
+        <v>-56</v>
       </c>
       <c r="I18" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" s="15">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="K18" s="14">
-        <v>-45.454545454545</v>
+        <v>-53.658536585365</v>
       </c>
       <c r="L18" s="14">
-        <v>-28</v>
+        <v>-34.482758620689</v>
       </c>
       <c r="M18" s="14">
-        <v>-60</v>
+        <v>-62.745098039215</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.898305084745</v>
+        <v>-94.722222222222</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,81 +1060,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D19" s="15">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E19" s="14">
-        <v>-9.090909090909</v>
+        <v>23.076923076923</v>
       </c>
       <c r="F19" s="15">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G19" s="15">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H19" s="14">
-        <v>-11.428571428571</v>
+        <v>-7.766990291262</v>
       </c>
       <c r="I19" s="15">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="J19" s="15">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="K19" s="14">
-        <v>-3.424657534246</v>
+        <v>-1.162790697674</v>
       </c>
       <c r="L19" s="14">
-        <v>-21.229050279329</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M19" s="14">
-        <v>10.15625</v>
+        <v>18.055555555555</v>
       </c>
       <c r="N19" s="14">
-        <v>-64.122137404580</v>
+        <v>-63.043478260869</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="15">
-        <v>1</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-100</v>
+      <c r="C20" s="15">
+        <v>2</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20" s="15">
+        <v>3</v>
+      </c>
+      <c r="H20" s="14">
+        <v>0</v>
+      </c>
+      <c r="I20" s="15">
         <v>5</v>
-      </c>
-      <c r="H20" s="14">
-        <v>-80</v>
-      </c>
-      <c r="I20" s="15">
-        <v>3</v>
       </c>
       <c r="J20" s="15">
         <v>6</v>
       </c>
       <c r="K20" s="14">
-        <v>-50</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L20" s="14">
         <v>0</v>
       </c>
       <c r="M20" s="14">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="N20" s="14">
-        <v>-99.238578680203</v>
+        <v>-98.951781970649</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E21" s="18">
-        <v>11.111111111111</v>
+        <v>-17.777777777777</v>
       </c>
       <c r="F21" s="17">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G21" s="17">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="H21" s="18">
-        <v>-16</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="I21" s="17">
-        <v>191</v>
+        <v>225</v>
       </c>
       <c r="J21" s="17">
-        <v>215</v>
+        <v>260</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.162790697674</v>
+        <v>-13.461538461538</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.416666666666</v>
+        <v>-16.974169741697</v>
       </c>
       <c r="M21" s="18">
-        <v>-6.829268292682</v>
+        <v>-2.597402597402</v>
       </c>
       <c r="N21" s="18">
-        <v>-84.732214228617</v>
+        <v>-84.868863483523</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1186,34 +1186,34 @@
         <v>2</v>
       </c>
       <c r="D22" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22" s="14">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F22" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G22" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H22" s="14">
         <v>-33.333333333333</v>
       </c>
       <c r="I22" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J22" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K22" s="14">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L22" s="14">
-        <v>-60</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M22" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1251,10 +1251,10 @@
         <v>50</v>
       </c>
       <c r="L23" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M23" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D24" s="15">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E24" s="14">
-        <v>-43.548387096774</v>
+        <v>-40</v>
       </c>
       <c r="F24" s="15">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="G24" s="15">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H24" s="14">
-        <v>-44.025157232704</v>
+        <v>-49.375</v>
       </c>
       <c r="I24" s="15">
-        <v>247</v>
+        <v>286</v>
       </c>
       <c r="J24" s="15">
-        <v>418</v>
+        <v>483</v>
       </c>
       <c r="K24" s="14">
-        <v>-40.909090909090</v>
+        <v>-40.786749482401</v>
       </c>
       <c r="L24" s="14">
-        <v>-27.777777777777</v>
+        <v>-24.934383202099</v>
       </c>
       <c r="M24" s="14">
-        <v>41.142857142857</v>
+        <v>40.886699507389</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D25" s="15">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E25" s="14">
-        <v>-60.714285714285</v>
+        <v>-49.056603773584</v>
       </c>
       <c r="F25" s="15">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="G25" s="15">
         <v>268</v>
       </c>
       <c r="H25" s="14">
-        <v>-50.746268656716</v>
+        <v>-57.462686567164</v>
       </c>
       <c r="I25" s="15">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="J25" s="15">
-        <v>343</v>
+        <v>396</v>
       </c>
       <c r="K25" s="14">
-        <v>-45.772594752186</v>
+        <v>-46.464646464646</v>
       </c>
       <c r="L25" s="14">
-        <v>-40.952380952380</v>
+        <v>-39.772727272727</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D26" s="15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E26" s="14">
-        <v>37.5</v>
+        <v>20</v>
       </c>
       <c r="F26" s="15">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G26" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H26" s="14">
-        <v>29.411764705882</v>
+        <v>50</v>
       </c>
       <c r="I26" s="15">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="J26" s="15">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K26" s="14">
-        <v>32</v>
+        <v>36.666666666666</v>
       </c>
       <c r="L26" s="14">
-        <v>-13.157894736842</v>
+        <v>0</v>
       </c>
       <c r="M26" s="14">
-        <v>-25</v>
+        <v>-21.153846153846</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="G27" s="15">
+        <v>1</v>
+      </c>
+      <c r="H27" s="14">
+        <v>0</v>
       </c>
       <c r="I27" s="15">
         <v>2</v>
       </c>
       <c r="J27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L27" s="14">
         <v>0</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="15">
         <v>2</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="15">
         <v>6</v>
       </c>
       <c r="H28" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J28" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K28" s="14">
-        <v>-72.727272727272</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="L28" s="14">
-        <v>-76.923076923076</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1554,29 +1554,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="15">
         <v>1</v>
       </c>
       <c r="G31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I31" s="15">
         <v>2</v>
       </c>
       <c r="J31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L31" s="14">
         <v>-33.333333333333</v>
@@ -1613,11 +1613,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="15">
-        <v>2</v>
-      </c>
-      <c r="E33" s="14">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-019pct.xlsx
+++ b/data/source/weekly/cs-en-us-019pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -898,11 +898,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N15" s="14">
         <v>-50</v>
@@ -936,41 +936,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" s="15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H16" s="14">
-        <v>-64.285714285714</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="I16" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J16" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K16" s="14">
-        <v>-57.142857142857</v>
+        <v>-52.173913043478</v>
       </c>
       <c r="L16" s="14">
-        <v>-62.5</v>
+        <v>-65.625</v>
       </c>
       <c r="M16" s="14">
-        <v>-55</v>
+        <v>-50</v>
       </c>
       <c r="N16" s="14">
-        <v>-94.339622641509</v>
+        <v>-93.956043956044</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>-50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F17" s="15">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G17" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H17" s="14">
-        <v>11.111111111111</v>
+        <v>27.272727272727</v>
       </c>
       <c r="I17" s="15">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J17" s="15">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K17" s="14">
-        <v>17.647058823529</v>
+        <v>20</v>
       </c>
       <c r="L17" s="14">
-        <v>185.714285714286</v>
+        <v>166.666666666667</v>
       </c>
       <c r="M17" s="14">
-        <v>122.222222222222</v>
+        <v>140</v>
       </c>
       <c r="N17" s="14">
-        <v>-23.076923076923</v>
+        <v>-14.285714285714</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E18" s="14">
-        <v>-87.5</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F18" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18" s="15">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H18" s="14">
-        <v>-56</v>
+        <v>-40</v>
       </c>
       <c r="I18" s="15">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J18" s="15">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="K18" s="14">
-        <v>-53.658536585365</v>
+        <v>-52.083333333333</v>
       </c>
       <c r="L18" s="14">
-        <v>-34.482758620689</v>
+        <v>-39.473684210526</v>
       </c>
       <c r="M18" s="14">
-        <v>-62.745098039215</v>
+        <v>-61.016949152542</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.722222222222</v>
+        <v>-94.362745098039</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" s="15">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E19" s="14">
-        <v>23.076923076923</v>
+        <v>72.222222222222</v>
       </c>
       <c r="F19" s="15">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="G19" s="15">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="H19" s="14">
-        <v>-7.766990291262</v>
+        <v>9.278350515463</v>
       </c>
       <c r="I19" s="15">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="J19" s="15">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="K19" s="14">
-        <v>-1.162790697674</v>
+        <v>5.789473684210</v>
       </c>
       <c r="L19" s="14">
-        <v>-16.666666666666</v>
+        <v>-10.666666666666</v>
       </c>
       <c r="M19" s="14">
-        <v>18.055555555555</v>
+        <v>23.312883435582</v>
       </c>
       <c r="N19" s="14">
-        <v>-63.043478260869</v>
+        <v>-61.859582542694</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
+        <v>3</v>
+      </c>
+      <c r="D20" s="15">
         <v>2</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="E20" s="14">
+        <v>50</v>
       </c>
       <c r="F20" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G20" s="15">
         <v>3</v>
       </c>
       <c r="H20" s="14">
+        <v>100</v>
+      </c>
+      <c r="I20" s="15">
+        <v>8</v>
+      </c>
+      <c r="J20" s="15">
+        <v>8</v>
+      </c>
+      <c r="K20" s="14">
         <v>0</v>
       </c>
-      <c r="I20" s="15">
-        <v>5</v>
-      </c>
-      <c r="J20" s="15">
-        <v>6</v>
-      </c>
-      <c r="K20" s="14">
-        <v>-16.666666666666</v>
-      </c>
       <c r="L20" s="14">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M20" s="14">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N20" s="14">
-        <v>-98.951781970649</v>
+        <v>-98.504672897196</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,75 +1142,75 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D21" s="17">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E21" s="18">
-        <v>-17.777777777777</v>
+        <v>37.5</v>
       </c>
       <c r="F21" s="17">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="G21" s="17">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="H21" s="18">
-        <v>-19.354838709677</v>
+        <v>-1.379310344827</v>
       </c>
       <c r="I21" s="17">
-        <v>225</v>
+        <v>269</v>
       </c>
       <c r="J21" s="17">
-        <v>260</v>
+        <v>292</v>
       </c>
       <c r="K21" s="18">
-        <v>-13.461538461538</v>
+        <v>-7.876712328767</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.974169741697</v>
+        <v>-14.057507987220</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.597402597402</v>
+        <v>2.281368821292</v>
       </c>
       <c r="N21" s="18">
-        <v>-84.868863483523</v>
+        <v>-84.035608308605</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>2</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" s="14">
-        <v>-33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="15">
         <v>4</v>
       </c>
       <c r="G22" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H22" s="14">
-        <v>-33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="I22" s="15">
         <v>4</v>
       </c>
       <c r="J22" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K22" s="14">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="L22" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="M22" s="14">
         <v>100</v>
@@ -1226,35 +1226,35 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="15">
+        <v>1</v>
+      </c>
+      <c r="E23" s="14">
+        <v>-100</v>
       </c>
       <c r="F23" s="15">
         <v>2</v>
       </c>
       <c r="G23" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I23" s="15">
         <v>3</v>
       </c>
       <c r="J23" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L23" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="M23" s="14">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D24" s="15">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="E24" s="14">
-        <v>-40</v>
+        <v>-15.686274509803</v>
       </c>
       <c r="F24" s="15">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="G24" s="15">
-        <v>320</v>
+        <v>262</v>
       </c>
       <c r="H24" s="14">
-        <v>-49.375</v>
+        <v>-41.984732824427</v>
       </c>
       <c r="I24" s="15">
-        <v>286</v>
+        <v>329</v>
       </c>
       <c r="J24" s="15">
-        <v>483</v>
+        <v>534</v>
       </c>
       <c r="K24" s="14">
-        <v>-40.786749482401</v>
+        <v>-38.389513108614</v>
       </c>
       <c r="L24" s="14">
-        <v>-24.934383202099</v>
+        <v>-22.405660377358</v>
       </c>
       <c r="M24" s="14">
-        <v>40.886699507389</v>
+        <v>48.868778280543</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D25" s="15">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E25" s="14">
-        <v>-49.056603773584</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="F25" s="15">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G25" s="15">
-        <v>268</v>
+        <v>228</v>
       </c>
       <c r="H25" s="14">
-        <v>-57.462686567164</v>
+        <v>-52.192982456140</v>
       </c>
       <c r="I25" s="15">
-        <v>212</v>
+        <v>246</v>
       </c>
       <c r="J25" s="15">
-        <v>396</v>
+        <v>442</v>
       </c>
       <c r="K25" s="14">
-        <v>-46.464646464646</v>
+        <v>-44.343891402714</v>
       </c>
       <c r="L25" s="14">
-        <v>-39.772727272727</v>
+        <v>-36.760925449871</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E26" s="14">
-        <v>20</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G26" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H26" s="14">
-        <v>50</v>
+        <v>36.842105263157</v>
       </c>
       <c r="I26" s="15">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J26" s="15">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K26" s="14">
-        <v>36.666666666666</v>
+        <v>39.393939393939</v>
       </c>
       <c r="L26" s="14">
-        <v>0</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="M26" s="14">
-        <v>-21.153846153846</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,11 +1390,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
@@ -1432,31 +1432,31 @@
         <v>1</v>
       </c>
       <c r="D28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H28" s="14">
-        <v>-33.333333333333</v>
+        <v>-37.5</v>
       </c>
       <c r="I28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" s="15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K28" s="14">
-        <v>-69.230769230769</v>
+        <v>-68.75</v>
       </c>
       <c r="L28" s="14">
-        <v>-71.428571428571</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1554,11 +1554,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="15">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-019pct.xlsx
+++ b/data/source/weekly/cs-en-us-019pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -881,8 +881,8 @@
       <c r="K14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>21</v>
+      <c r="L14" s="14">
+        <v>-100</v>
       </c>
       <c r="M14" s="14">
         <v>-100</v>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,31 +905,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="15">
         <v>3</v>
       </c>
       <c r="K15" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L15" s="14">
         <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N15" s="14">
-        <v>-50</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="F16" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H16" s="14">
-        <v>-69.230769230769</v>
+        <v>-78.571428571428</v>
       </c>
       <c r="I16" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J16" s="15">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K16" s="14">
-        <v>-52.173913043478</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L16" s="14">
-        <v>-65.625</v>
+        <v>-64.705882352941</v>
       </c>
       <c r="M16" s="14">
-        <v>-50</v>
+        <v>-47.826086956521</v>
       </c>
       <c r="N16" s="14">
-        <v>-93.956043956044</v>
+        <v>-94.230769230769</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -981,37 +981,37 @@
         <v>4</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E17" s="14">
-        <v>33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="F17" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G17" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H17" s="14">
-        <v>27.272727272727</v>
+        <v>15.384615384615</v>
       </c>
       <c r="I17" s="15">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J17" s="15">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K17" s="14">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="L17" s="14">
-        <v>166.666666666667</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M17" s="14">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="N17" s="14">
-        <v>-14.285714285714</v>
+        <v>-22.222222222222</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E18" s="14">
-        <v>-42.857142857142</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G18" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H18" s="14">
-        <v>-40</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="I18" s="15">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J18" s="15">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K18" s="14">
-        <v>-52.083333333333</v>
+        <v>-47.169811320754</v>
       </c>
       <c r="L18" s="14">
-        <v>-39.473684210526</v>
+        <v>-40.425531914893</v>
       </c>
       <c r="M18" s="14">
-        <v>-61.016949152542</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.362745098039</v>
+        <v>-93.763919821826</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,81 +1060,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
+        <v>30</v>
+      </c>
+      <c r="D19" s="15">
         <v>31</v>
       </c>
-      <c r="D19" s="15">
-        <v>18</v>
-      </c>
       <c r="E19" s="14">
-        <v>72.222222222222</v>
+        <v>-3.225806451612</v>
       </c>
       <c r="F19" s="15">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="G19" s="15">
         <v>97</v>
       </c>
       <c r="H19" s="14">
-        <v>9.278350515463</v>
+        <v>16.494845360824</v>
       </c>
       <c r="I19" s="15">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="J19" s="15">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="K19" s="14">
-        <v>5.789473684210</v>
+        <v>4.524886877828</v>
       </c>
       <c r="L19" s="14">
-        <v>-10.666666666666</v>
+        <v>-10.465116279069</v>
       </c>
       <c r="M19" s="14">
-        <v>23.312883435582</v>
+        <v>20.3125</v>
       </c>
       <c r="N19" s="14">
-        <v>-61.859582542694</v>
+        <v>-62.131147540983</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>3</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G20" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" s="14">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I20" s="15">
         <v>8</v>
       </c>
       <c r="J20" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K20" s="14">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L20" s="14">
-        <v>14.285714285714</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M20" s="14">
         <v>33.333333333333</v>
       </c>
       <c r="N20" s="14">
-        <v>-98.504672897196</v>
+        <v>-98.699186991869</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D21" s="17">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E21" s="18">
-        <v>37.5</v>
+        <v>-12.765957446808</v>
       </c>
       <c r="F21" s="17">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="G21" s="17">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="H21" s="18">
-        <v>-1.379310344827</v>
+        <v>0.662251655629</v>
       </c>
       <c r="I21" s="17">
-        <v>269</v>
+        <v>310</v>
       </c>
       <c r="J21" s="17">
-        <v>292</v>
+        <v>339</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.876712328767</v>
+        <v>-8.554572271386</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.057507987220</v>
+        <v>-14.835164835164</v>
       </c>
       <c r="M21" s="18">
-        <v>2.281368821292</v>
+        <v>4.377104377104</v>
       </c>
       <c r="N21" s="18">
-        <v>-84.035608308605</v>
+        <v>-83.879355174207</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1185,11 +1185,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
         <v>4</v>
@@ -1232,26 +1232,26 @@
       <c r="E23" s="14">
         <v>-100</v>
       </c>
-      <c r="F23" s="15">
-        <v>2</v>
+      <c r="F23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G23" s="15">
         <v>2</v>
       </c>
       <c r="H23" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I23" s="15">
         <v>3</v>
       </c>
       <c r="J23" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="L23" s="14">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="M23" s="14">
         <v>-40</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
+        <v>50</v>
+      </c>
+      <c r="D24" s="15">
         <v>43</v>
       </c>
-      <c r="D24" s="15">
-        <v>51</v>
-      </c>
       <c r="E24" s="14">
-        <v>-15.686274509803</v>
+        <v>16.279069767441</v>
       </c>
       <c r="F24" s="15">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="G24" s="15">
-        <v>262</v>
+        <v>221</v>
       </c>
       <c r="H24" s="14">
-        <v>-41.984732824427</v>
+        <v>-24.434389140271</v>
       </c>
       <c r="I24" s="15">
-        <v>329</v>
+        <v>379</v>
       </c>
       <c r="J24" s="15">
-        <v>534</v>
+        <v>577</v>
       </c>
       <c r="K24" s="14">
-        <v>-38.389513108614</v>
+        <v>-34.315424610052</v>
       </c>
       <c r="L24" s="14">
-        <v>-22.405660377358</v>
+        <v>-20.876826722338</v>
       </c>
       <c r="M24" s="14">
-        <v>48.868778280543</v>
+        <v>52.822580645161</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D25" s="15">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E25" s="14">
-        <v>-26.086956521739</v>
+        <v>-2.272727272727</v>
       </c>
       <c r="F25" s="15">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="G25" s="15">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="H25" s="14">
-        <v>-52.192982456140</v>
+        <v>-36.683417085427</v>
       </c>
       <c r="I25" s="15">
-        <v>246</v>
+        <v>288</v>
       </c>
       <c r="J25" s="15">
-        <v>442</v>
+        <v>486</v>
       </c>
       <c r="K25" s="14">
-        <v>-44.343891402714</v>
+        <v>-40.740740740740</v>
       </c>
       <c r="L25" s="14">
-        <v>-36.760925449871</v>
+        <v>-34.988713318284</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1350,34 +1350,34 @@
         <v>5</v>
       </c>
       <c r="D26" s="15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E26" s="14">
-        <v>66.666666666666</v>
+        <v>-37.5</v>
       </c>
       <c r="F26" s="15">
         <v>26</v>
       </c>
       <c r="G26" s="15">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H26" s="14">
-        <v>36.842105263157</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I26" s="15">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J26" s="15">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="K26" s="14">
-        <v>39.393939393939</v>
+        <v>21.951219512195</v>
       </c>
       <c r="L26" s="14">
-        <v>-4.166666666666</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="M26" s="14">
-        <v>-20.689655172413</v>
+        <v>-18.032786885245</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,22 +1397,22 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="15">
         <v>3</v>
       </c>
       <c r="K27" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L27" s="14">
         <v>0</v>
@@ -1428,23 +1428,23 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="15">
-        <v>3</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-66.666666666666</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H28" s="14">
-        <v>-37.5</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I28" s="15">
         <v>5</v>
@@ -1456,7 +1456,7 @@
         <v>-68.75</v>
       </c>
       <c r="L28" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1496,8 +1496,8 @@
       <c r="K29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
+      <c r="L29" s="14">
+        <v>-100</v>
       </c>
       <c r="M29" s="14">
         <v>-100</v>
@@ -1537,8 +1537,8 @@
       <c r="K30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L30" s="13" t="s">
-        <v>21</v>
+      <c r="L30" s="14">
+        <v>-100</v>
       </c>
       <c r="M30" s="14">
         <v>-100</v>
@@ -1554,32 +1554,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="15">
+      <c r="D31" s="15">
         <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="15">
         <v>2</v>
       </c>
       <c r="H31" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I31" s="15">
         <v>2</v>
       </c>
       <c r="J31" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L31" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-019pct.xlsx
+++ b/data/source/weekly/cs-en-us-019pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -895,32 +895,32 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="15">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="15">
+      <c r="G15" s="15">
         <v>2</v>
       </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
       <c r="H15" s="14">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="15">
         <v>3</v>
       </c>
       <c r="J15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="L15" s="14">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>50</v>
       </c>
       <c r="N15" s="14">
-        <v>-25</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E16" s="14">
-        <v>-80</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F16" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G16" s="15">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H16" s="14">
-        <v>-78.571428571428</v>
+        <v>-70</v>
       </c>
       <c r="I16" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J16" s="15">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K16" s="14">
         <v>-57.142857142857</v>
       </c>
       <c r="L16" s="14">
-        <v>-64.705882352941</v>
+        <v>-60.526315789473</v>
       </c>
       <c r="M16" s="14">
-        <v>-47.826086956521</v>
+        <v>-40</v>
       </c>
       <c r="N16" s="14">
-        <v>-94.230769230769</v>
+        <v>-93.927125506072</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D17" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14">
-        <v>-20</v>
+        <v>50</v>
       </c>
       <c r="F17" s="15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G17" s="15">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H17" s="14">
-        <v>15.384615384615</v>
+        <v>0</v>
       </c>
       <c r="I17" s="15">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="J17" s="15">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K17" s="14">
-        <v>12</v>
+        <v>19.354838709677</v>
       </c>
       <c r="L17" s="14">
-        <v>133.333333333333</v>
+        <v>105.555555555556</v>
       </c>
       <c r="M17" s="14">
-        <v>180</v>
+        <v>146.666666666667</v>
       </c>
       <c r="N17" s="14">
-        <v>-22.222222222222</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D18" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F18" s="15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18" s="15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H18" s="14">
-        <v>-36.363636363636</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="I18" s="15">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J18" s="15">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K18" s="14">
-        <v>-47.169811320754</v>
+        <v>-42.592592592592</v>
       </c>
       <c r="L18" s="14">
-        <v>-40.425531914893</v>
+        <v>-36.734693877551</v>
       </c>
       <c r="M18" s="14">
-        <v>-55.555555555555</v>
+        <v>-55.072463768115</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.763919821826</v>
+        <v>-93.621399176954</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,81 +1060,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D19" s="15">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E19" s="14">
-        <v>-3.225806451612</v>
+        <v>6.25</v>
       </c>
       <c r="F19" s="15">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="G19" s="15">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="H19" s="14">
-        <v>16.494845360824</v>
+        <v>18.691588785046</v>
       </c>
       <c r="I19" s="15">
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="J19" s="15">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="K19" s="14">
-        <v>4.524886877828</v>
+        <v>4.743083003952</v>
       </c>
       <c r="L19" s="14">
-        <v>-10.465116279069</v>
+        <v>-8.934707903780</v>
       </c>
       <c r="M19" s="14">
-        <v>20.3125</v>
+        <v>17.777777777777</v>
       </c>
       <c r="N19" s="14">
-        <v>-62.131147540983</v>
+        <v>-61.257309941520</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="15">
+      <c r="C20" s="15">
         <v>1</v>
       </c>
-      <c r="E20" s="14">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20" s="14">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="I20" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J20" s="15">
         <v>9</v>
       </c>
       <c r="K20" s="14">
-        <v>-11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="L20" s="14">
-        <v>-11.111111111111</v>
+        <v>-10</v>
       </c>
       <c r="M20" s="14">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="N20" s="14">
-        <v>-98.699186991869</v>
+        <v>-98.689956331877</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,78 +1142,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D21" s="17">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E21" s="18">
-        <v>-12.765957446808</v>
+        <v>8.695652173913</v>
       </c>
       <c r="F21" s="17">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="G21" s="17">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="H21" s="18">
-        <v>0.662251655629</v>
+        <v>0</v>
       </c>
       <c r="I21" s="17">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="J21" s="17">
-        <v>339</v>
+        <v>386</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.554572271386</v>
+        <v>-6.735751295336</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.835164835164</v>
+        <v>-12.195121951219</v>
       </c>
       <c r="M21" s="18">
-        <v>4.377104377104</v>
+        <v>4.956268221574</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.879355174207</v>
+        <v>-83.255813953488</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="15">
+        <v>3</v>
+      </c>
+      <c r="D22" s="15">
+        <v>2</v>
+      </c>
+      <c r="E22" s="14">
+        <v>50</v>
       </c>
       <c r="F22" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H22" s="14">
-        <v>-20</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I22" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J22" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K22" s="14">
-        <v>-50</v>
+        <v>-30</v>
       </c>
       <c r="L22" s="14">
-        <v>-50</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M22" s="14">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1236,7 +1236,7 @@
         <v>20</v>
       </c>
       <c r="G23" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23" s="14">
         <v>-100</v>
@@ -1245,16 +1245,16 @@
         <v>3</v>
       </c>
       <c r="J23" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K23" s="14">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="L23" s="14">
+        <v>-57.142857142857</v>
+      </c>
+      <c r="M23" s="14">
         <v>-50</v>
-      </c>
-      <c r="M23" s="14">
-        <v>-40</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D24" s="15">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="E24" s="14">
-        <v>16.279069767441</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="F24" s="15">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="G24" s="15">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="H24" s="14">
-        <v>-24.434389140271</v>
+        <v>-18.309859154929</v>
       </c>
       <c r="I24" s="15">
-        <v>379</v>
+        <v>420</v>
       </c>
       <c r="J24" s="15">
-        <v>577</v>
+        <v>631</v>
       </c>
       <c r="K24" s="14">
-        <v>-34.315424610052</v>
+        <v>-33.438985736925</v>
       </c>
       <c r="L24" s="14">
-        <v>-20.876826722338</v>
+        <v>-20.604914933837</v>
       </c>
       <c r="M24" s="14">
-        <v>52.822580645161</v>
+        <v>49.466192170818</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="D25" s="15">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="E25" s="14">
-        <v>-2.272727272727</v>
+        <v>-51.666666666666</v>
       </c>
       <c r="F25" s="15">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G25" s="15">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="H25" s="14">
-        <v>-36.683417085427</v>
+        <v>-34.482758620689</v>
       </c>
       <c r="I25" s="15">
-        <v>288</v>
+        <v>317</v>
       </c>
       <c r="J25" s="15">
-        <v>486</v>
+        <v>546</v>
       </c>
       <c r="K25" s="14">
-        <v>-40.740740740740</v>
+        <v>-41.941391941391</v>
       </c>
       <c r="L25" s="14">
-        <v>-34.988713318284</v>
+        <v>-34.232365145228</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D26" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E26" s="14">
-        <v>-37.5</v>
+        <v>20</v>
       </c>
       <c r="F26" s="15">
+        <v>27</v>
+      </c>
+      <c r="G26" s="15">
         <v>26</v>
       </c>
-      <c r="G26" s="15">
-        <v>24</v>
-      </c>
       <c r="H26" s="14">
-        <v>8.333333333333</v>
+        <v>3.846153846153</v>
       </c>
       <c r="I26" s="15">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="J26" s="15">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="K26" s="14">
-        <v>21.951219512195</v>
+        <v>19.607843137254</v>
       </c>
       <c r="L26" s="14">
-        <v>-10.714285714285</v>
+        <v>1.666666666666</v>
       </c>
       <c r="M26" s="14">
-        <v>-18.032786885245</v>
+        <v>-3.174603174603</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="15">
+      <c r="G27" s="15">
         <v>2</v>
       </c>
-      <c r="G27" s="15">
-        <v>1</v>
-      </c>
       <c r="H27" s="14">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="15">
         <v>3</v>
       </c>
       <c r="J27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="L27" s="14">
         <v>0</v>
@@ -1428,8 +1428,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1438,25 +1438,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="15">
+        <v>3</v>
+      </c>
+      <c r="G28" s="15">
         <v>4</v>
       </c>
-      <c r="G28" s="15">
-        <v>7</v>
-      </c>
       <c r="H28" s="14">
-        <v>-42.857142857142</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" s="15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K28" s="14">
-        <v>-68.75</v>
+        <v>-60</v>
       </c>
       <c r="L28" s="14">
-        <v>-75</v>
+        <v>-76</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1554,11 +1554,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1579,7 +1579,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L31" s="14">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1622,11 +1622,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="15">
-        <v>2</v>
-      </c>
-      <c r="H33" s="14">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-019pct.xlsx
+++ b/data/source/weekly/cs-en-us-019pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -908,10 +908,10 @@
         <v>1</v>
       </c>
       <c r="G15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
         <v>3</v>
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D16" s="15">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>-57.142857142857</v>
+        <v>600</v>
       </c>
       <c r="F16" s="15">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G16" s="15">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H16" s="14">
-        <v>-70</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I16" s="15">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J16" s="15">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K16" s="14">
-        <v>-57.142857142857</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="L16" s="14">
-        <v>-60.526315789473</v>
+        <v>-48.837209302325</v>
       </c>
       <c r="M16" s="14">
-        <v>-40</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="N16" s="14">
-        <v>-93.927125506072</v>
+        <v>-91.911764705882</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,13 +978,13 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D17" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E17" s="14">
-        <v>50</v>
+        <v>-75</v>
       </c>
       <c r="F17" s="15">
         <v>18</v>
@@ -996,22 +996,22 @@
         <v>0</v>
       </c>
       <c r="I17" s="15">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J17" s="15">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K17" s="14">
-        <v>19.354838709677</v>
+        <v>11.428571428571</v>
       </c>
       <c r="L17" s="14">
-        <v>105.555555555556</v>
+        <v>77.272727272727</v>
       </c>
       <c r="M17" s="14">
-        <v>146.666666666667</v>
+        <v>105.263157894737</v>
       </c>
       <c r="N17" s="14">
-        <v>-7.5</v>
+        <v>-18.75</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" s="14">
-        <v>200</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="15">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H18" s="14">
-        <v>-38.095238095238</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="I18" s="15">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J18" s="15">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K18" s="14">
-        <v>-42.592592592592</v>
+        <v>-43.103448275862</v>
       </c>
       <c r="L18" s="14">
-        <v>-36.734693877551</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="M18" s="14">
-        <v>-55.072463768115</v>
+        <v>-55.405405405405</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.621399176954</v>
+        <v>-93.866171003717</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D19" s="15">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E19" s="14">
-        <v>6.25</v>
+        <v>-36.666666666666</v>
       </c>
       <c r="F19" s="15">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="G19" s="15">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H19" s="14">
-        <v>18.691588785046</v>
+        <v>2.702702702702</v>
       </c>
       <c r="I19" s="15">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="J19" s="15">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="K19" s="14">
-        <v>4.743083003952</v>
+        <v>0.353356890459</v>
       </c>
       <c r="L19" s="14">
-        <v>-8.934707903780</v>
+        <v>-10.126582278481</v>
       </c>
       <c r="M19" s="14">
-        <v>17.777777777777</v>
+        <v>14.056224899598</v>
       </c>
       <c r="N19" s="14">
-        <v>-61.257309941520</v>
+        <v>-61.879194630872</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="D20" s="15">
+        <v>3</v>
+      </c>
+      <c r="E20" s="14">
+        <v>33.333333333333</v>
       </c>
       <c r="F20" s="15">
+        <v>8</v>
+      </c>
+      <c r="G20" s="15">
         <v>6</v>
       </c>
-      <c r="G20" s="15">
-        <v>3</v>
-      </c>
       <c r="H20" s="14">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I20" s="15">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J20" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K20" s="14">
+        <v>8.333333333333</v>
+      </c>
+      <c r="L20" s="14">
         <v>0</v>
       </c>
-      <c r="L20" s="14">
-        <v>-10</v>
-      </c>
       <c r="M20" s="14">
-        <v>50</v>
+        <v>85.714285714285</v>
       </c>
       <c r="N20" s="14">
-        <v>-98.689956331877</v>
+        <v>-98.214285714285</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="D21" s="17">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E21" s="18">
-        <v>8.695652173913</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="F21" s="17">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G21" s="17">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H21" s="18">
         <v>0</v>
       </c>
       <c r="I21" s="17">
-        <v>360</v>
+        <v>394</v>
       </c>
       <c r="J21" s="17">
-        <v>386</v>
+        <v>428</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.735751295336</v>
+        <v>-7.943925233644</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.195121951219</v>
+        <v>-12.831858407079</v>
       </c>
       <c r="M21" s="18">
-        <v>4.956268221574</v>
+        <v>4.232804232804</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.255813953488</v>
+        <v>-83.140778776208</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,37 +1183,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F22" s="15">
         <v>5</v>
       </c>
       <c r="G22" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H22" s="14">
-        <v>-16.666666666666</v>
+        <v>25</v>
       </c>
       <c r="I22" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J22" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K22" s="14">
-        <v>-30</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L22" s="14">
-        <v>-22.222222222222</v>
+        <v>-10</v>
       </c>
       <c r="M22" s="14">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1227,7 +1227,7 @@
         <v>20</v>
       </c>
       <c r="D23" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="14">
         <v>-100</v>
@@ -1236,7 +1236,7 @@
         <v>20</v>
       </c>
       <c r="G23" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H23" s="14">
         <v>-100</v>
@@ -1245,16 +1245,16 @@
         <v>3</v>
       </c>
       <c r="J23" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K23" s="14">
-        <v>-50</v>
+        <v>-62.5</v>
       </c>
       <c r="L23" s="14">
         <v>-57.142857142857</v>
       </c>
       <c r="M23" s="14">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D24" s="15">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E24" s="14">
-        <v>-27.777777777777</v>
+        <v>-12.727272727272</v>
       </c>
       <c r="F24" s="15">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="G24" s="15">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="H24" s="14">
-        <v>-18.309859154929</v>
+        <v>-9.852216748768</v>
       </c>
       <c r="I24" s="15">
-        <v>420</v>
+        <v>468</v>
       </c>
       <c r="J24" s="15">
-        <v>631</v>
+        <v>686</v>
       </c>
       <c r="K24" s="14">
-        <v>-33.438985736925</v>
+        <v>-31.778425655976</v>
       </c>
       <c r="L24" s="14">
-        <v>-20.604914933837</v>
+        <v>-19.310344827586</v>
       </c>
       <c r="M24" s="14">
-        <v>49.466192170818</v>
+        <v>52.442996742671</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D25" s="15">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E25" s="14">
-        <v>-51.666666666666</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F25" s="15">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G25" s="15">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="H25" s="14">
-        <v>-34.482758620689</v>
+        <v>-30.927835051546</v>
       </c>
       <c r="I25" s="15">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="J25" s="15">
-        <v>546</v>
+        <v>590</v>
       </c>
       <c r="K25" s="14">
-        <v>-41.941391941391</v>
+        <v>-41.525423728813</v>
       </c>
       <c r="L25" s="14">
-        <v>-34.232365145228</v>
+        <v>-34.659090909090</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D26" s="15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E26" s="14">
-        <v>20</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F26" s="15">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G26" s="15">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H26" s="14">
-        <v>3.846153846153</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I26" s="15">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J26" s="15">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="K26" s="14">
-        <v>19.607843137254</v>
+        <v>10.344827586206</v>
       </c>
       <c r="L26" s="14">
-        <v>1.666666666666</v>
+        <v>-3.030303030303</v>
       </c>
       <c r="M26" s="14">
-        <v>-3.174603174603</v>
+        <v>-7.246376811594</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,11 +1390,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
@@ -1409,10 +1409,10 @@
         <v>3</v>
       </c>
       <c r="J27" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27" s="14">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="L27" s="14">
         <v>0</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
+        <v>2</v>
+      </c>
+      <c r="D28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="14">
+        <v>100</v>
       </c>
       <c r="F28" s="15">
+        <v>4</v>
+      </c>
+      <c r="G28" s="15">
         <v>3</v>
       </c>
-      <c r="G28" s="15">
-        <v>4</v>
-      </c>
       <c r="H28" s="14">
-        <v>-25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I28" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J28" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K28" s="14">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="L28" s="14">
-        <v>-76</v>
+        <v>-68</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="G31" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="14">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-019pct.xlsx
+++ b/data/source/weekly/cs-en-us-019pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -567,7 +567,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -863,8 +863,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -872,8 +872,8 @@
       <c r="H14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>20</v>
@@ -881,14 +881,14 @@
       <c r="K14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="14">
-        <v>-100</v>
-      </c>
-      <c r="M14" s="14">
-        <v>-100</v>
-      </c>
-      <c r="N14" s="14">
-        <v>-100</v>
+      <c r="L14" s="15">
+        <v>0</v>
+      </c>
+      <c r="M14" s="15">
+        <v>0</v>
+      </c>
+      <c r="N14" s="15">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -904,31 +904,31 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="14">
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="14">
+        <v>3</v>
+      </c>
+      <c r="J15" s="14">
+        <v>4</v>
+      </c>
+      <c r="K15" s="15">
+        <v>-25</v>
+      </c>
+      <c r="L15" s="15">
         <v>0</v>
       </c>
-      <c r="I15" s="15">
-        <v>3</v>
-      </c>
-      <c r="J15" s="15">
-        <v>4</v>
-      </c>
-      <c r="K15" s="14">
-        <v>-25</v>
-      </c>
-      <c r="L15" s="14">
+      <c r="M15" s="15">
         <v>0</v>
       </c>
-      <c r="M15" s="14">
-        <v>50</v>
-      </c>
-      <c r="N15" s="14">
+      <c r="N15" s="15">
         <v>-40</v>
       </c>
     </row>
@@ -936,205 +936,205 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>7</v>
-      </c>
-      <c r="D16" s="15">
-        <v>1</v>
-      </c>
-      <c r="E16" s="14">
-        <v>600</v>
-      </c>
-      <c r="F16" s="15">
+      <c r="C16" s="14">
+        <v>4</v>
+      </c>
+      <c r="D16" s="14">
+        <v>4</v>
+      </c>
+      <c r="E16" s="15">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14">
         <v>13</v>
       </c>
-      <c r="G16" s="15">
-        <v>15</v>
-      </c>
-      <c r="H16" s="14">
-        <v>-13.333333333333</v>
-      </c>
-      <c r="I16" s="15">
-        <v>22</v>
-      </c>
-      <c r="J16" s="15">
-        <v>36</v>
-      </c>
-      <c r="K16" s="14">
-        <v>-38.888888888888</v>
-      </c>
-      <c r="L16" s="14">
-        <v>-48.837209302325</v>
-      </c>
-      <c r="M16" s="14">
-        <v>-15.384615384615</v>
-      </c>
-      <c r="N16" s="14">
-        <v>-91.911764705882</v>
+      <c r="G16" s="14">
+        <v>17</v>
+      </c>
+      <c r="H16" s="15">
+        <v>-23.529411764705</v>
+      </c>
+      <c r="I16" s="14">
+        <v>24</v>
+      </c>
+      <c r="J16" s="14">
+        <v>40</v>
+      </c>
+      <c r="K16" s="15">
+        <v>-40</v>
+      </c>
+      <c r="L16" s="15">
+        <v>-45.454545454545</v>
+      </c>
+      <c r="M16" s="15">
+        <v>-14.285714285714</v>
+      </c>
+      <c r="N16" s="15">
+        <v>-91.808873720136</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>1</v>
-      </c>
-      <c r="D17" s="15">
+      <c r="C17" s="14">
         <v>4</v>
       </c>
-      <c r="E17" s="14">
-        <v>-75</v>
-      </c>
-      <c r="F17" s="15">
+      <c r="D17" s="14">
+        <v>3</v>
+      </c>
+      <c r="E17" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="F17" s="14">
         <v>18</v>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="14">
         <v>18</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H17" s="15">
         <v>0</v>
       </c>
-      <c r="I17" s="15">
-        <v>39</v>
-      </c>
-      <c r="J17" s="15">
-        <v>35</v>
-      </c>
-      <c r="K17" s="14">
-        <v>11.428571428571</v>
-      </c>
-      <c r="L17" s="14">
-        <v>77.272727272727</v>
-      </c>
-      <c r="M17" s="14">
-        <v>105.263157894737</v>
-      </c>
-      <c r="N17" s="14">
-        <v>-18.75</v>
+      <c r="I17" s="14">
+        <v>43</v>
+      </c>
+      <c r="J17" s="14">
+        <v>38</v>
+      </c>
+      <c r="K17" s="15">
+        <v>13.157894736842</v>
+      </c>
+      <c r="L17" s="15">
+        <v>53.571428571428</v>
+      </c>
+      <c r="M17" s="15">
+        <v>95.454545454545</v>
+      </c>
+      <c r="N17" s="15">
+        <v>-15.686274509803</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>2</v>
-      </c>
-      <c r="D18" s="15">
-        <v>4</v>
-      </c>
-      <c r="E18" s="14">
-        <v>-50</v>
-      </c>
-      <c r="F18" s="15">
-        <v>14</v>
-      </c>
-      <c r="G18" s="15">
-        <v>17</v>
-      </c>
-      <c r="H18" s="14">
-        <v>-17.647058823529</v>
-      </c>
-      <c r="I18" s="15">
-        <v>33</v>
-      </c>
-      <c r="J18" s="15">
-        <v>58</v>
-      </c>
-      <c r="K18" s="14">
-        <v>-43.103448275862</v>
-      </c>
-      <c r="L18" s="14">
-        <v>-38.888888888888</v>
-      </c>
-      <c r="M18" s="14">
-        <v>-55.405405405405</v>
-      </c>
-      <c r="N18" s="14">
-        <v>-93.866171003717</v>
+      <c r="C18" s="14">
+        <v>3</v>
+      </c>
+      <c r="D18" s="14">
+        <v>8</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-62.5</v>
+      </c>
+      <c r="F18" s="14">
+        <v>13</v>
+      </c>
+      <c r="G18" s="14">
+        <v>18</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-27.777777777777</v>
+      </c>
+      <c r="I18" s="14">
+        <v>36</v>
+      </c>
+      <c r="J18" s="14">
+        <v>66</v>
+      </c>
+      <c r="K18" s="15">
+        <v>-45.454545454545</v>
+      </c>
+      <c r="L18" s="15">
+        <v>-36.842105263157</v>
+      </c>
+      <c r="M18" s="15">
+        <v>-52.631578947368</v>
+      </c>
+      <c r="N18" s="15">
+        <v>-93.939393939393</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15">
-        <v>19</v>
-      </c>
-      <c r="D19" s="15">
-        <v>30</v>
-      </c>
-      <c r="E19" s="14">
-        <v>-36.666666666666</v>
-      </c>
-      <c r="F19" s="15">
-        <v>114</v>
-      </c>
-      <c r="G19" s="15">
+      <c r="C19" s="14">
+        <v>27</v>
+      </c>
+      <c r="D19" s="14">
+        <v>40</v>
+      </c>
+      <c r="E19" s="15">
+        <v>-32.5</v>
+      </c>
+      <c r="F19" s="14">
         <v>111</v>
       </c>
-      <c r="H19" s="14">
-        <v>2.702702702702</v>
-      </c>
-      <c r="I19" s="15">
-        <v>284</v>
-      </c>
-      <c r="J19" s="15">
-        <v>283</v>
-      </c>
-      <c r="K19" s="14">
-        <v>0.353356890459</v>
-      </c>
-      <c r="L19" s="14">
-        <v>-10.126582278481</v>
-      </c>
-      <c r="M19" s="14">
-        <v>14.056224899598</v>
-      </c>
-      <c r="N19" s="14">
-        <v>-61.879194630872</v>
+      <c r="G19" s="14">
+        <v>133</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-16.541353383458</v>
+      </c>
+      <c r="I19" s="14">
+        <v>312</v>
+      </c>
+      <c r="J19" s="14">
+        <v>323</v>
+      </c>
+      <c r="K19" s="15">
+        <v>-3.405572755417</v>
+      </c>
+      <c r="L19" s="15">
+        <v>-12.112676056338</v>
+      </c>
+      <c r="M19" s="15">
+        <v>15.985130111524</v>
+      </c>
+      <c r="N19" s="15">
+        <v>-62.043795620438</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="14">
+        <v>6</v>
+      </c>
+      <c r="G20" s="14">
         <v>4</v>
       </c>
-      <c r="D20" s="15">
-        <v>3</v>
-      </c>
-      <c r="E20" s="14">
-        <v>33.333333333333</v>
-      </c>
-      <c r="F20" s="15">
-        <v>8</v>
-      </c>
-      <c r="G20" s="15">
-        <v>6</v>
-      </c>
-      <c r="H20" s="14">
-        <v>33.333333333333</v>
-      </c>
-      <c r="I20" s="15">
-        <v>13</v>
-      </c>
-      <c r="J20" s="15">
+      <c r="H20" s="15">
+        <v>50</v>
+      </c>
+      <c r="I20" s="14">
+        <v>14</v>
+      </c>
+      <c r="J20" s="14">
         <v>12</v>
       </c>
-      <c r="K20" s="14">
-        <v>8.333333333333</v>
-      </c>
-      <c r="L20" s="14">
-        <v>0</v>
-      </c>
-      <c r="M20" s="14">
-        <v>85.714285714285</v>
-      </c>
-      <c r="N20" s="14">
-        <v>-98.214285714285</v>
+      <c r="K20" s="15">
+        <v>16.666666666666</v>
+      </c>
+      <c r="L20" s="15">
+        <v>7.692307692307</v>
+      </c>
+      <c r="M20" s="15">
+        <v>100</v>
+      </c>
+      <c r="N20" s="15">
+        <v>-98.202824133504</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,77 +1142,77 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D21" s="17">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E21" s="18">
-        <v>-21.428571428571</v>
+        <v>-29.090909090909</v>
       </c>
       <c r="F21" s="17">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G21" s="17">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="H21" s="18">
-        <v>0</v>
+        <v>-14.210526315789</v>
       </c>
       <c r="I21" s="17">
-        <v>394</v>
+        <v>433</v>
       </c>
       <c r="J21" s="17">
-        <v>428</v>
+        <v>483</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.943925233644</v>
+        <v>-10.351966873706</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.831858407079</v>
+        <v>-13.572854291417</v>
       </c>
       <c r="M21" s="18">
-        <v>4.232804232804</v>
+        <v>6.650246305418</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.140778776208</v>
+        <v>-82.986247544204</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
-      </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>0</v>
-      </c>
-      <c r="F22" s="15">
-        <v>5</v>
-      </c>
-      <c r="G22" s="15">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
         <v>4</v>
       </c>
-      <c r="H22" s="14">
-        <v>25</v>
-      </c>
-      <c r="I22" s="15">
+      <c r="G22" s="14">
+        <v>3</v>
+      </c>
+      <c r="H22" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="I22" s="14">
         <v>9</v>
       </c>
-      <c r="J22" s="15">
+      <c r="J22" s="14">
         <v>11</v>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="15">
         <v>-18.181818181818</v>
       </c>
-      <c r="L22" s="14">
+      <c r="L22" s="15">
         <v>-10</v>
       </c>
-      <c r="M22" s="14">
+      <c r="M22" s="15">
         <v>350</v>
       </c>
       <c r="N22" s="13" t="s">
@@ -1223,38 +1223,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="15">
-        <v>2</v>
-      </c>
-      <c r="E23" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="15">
-        <v>6</v>
-      </c>
-      <c r="H23" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I23" s="15">
-        <v>3</v>
-      </c>
-      <c r="J23" s="15">
-        <v>8</v>
-      </c>
-      <c r="K23" s="14">
-        <v>-62.5</v>
-      </c>
-      <c r="L23" s="14">
-        <v>-57.142857142857</v>
-      </c>
-      <c r="M23" s="14">
-        <v>-57.142857142857</v>
+      <c r="C23" s="14">
+        <v>1</v>
+      </c>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>0</v>
+      </c>
+      <c r="F23" s="14">
+        <v>1</v>
+      </c>
+      <c r="G23" s="14">
+        <v>5</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-80</v>
+      </c>
+      <c r="I23" s="14">
+        <v>4</v>
+      </c>
+      <c r="J23" s="14">
+        <v>9</v>
+      </c>
+      <c r="K23" s="15">
+        <v>-55.555555555555</v>
+      </c>
+      <c r="L23" s="15">
+        <v>-42.857142857142</v>
+      </c>
+      <c r="M23" s="15">
+        <v>-50</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1264,38 +1264,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
-        <v>48</v>
-      </c>
-      <c r="D24" s="15">
-        <v>55</v>
-      </c>
-      <c r="E24" s="14">
-        <v>-12.727272727272</v>
-      </c>
-      <c r="F24" s="15">
-        <v>183</v>
-      </c>
-      <c r="G24" s="15">
-        <v>203</v>
-      </c>
-      <c r="H24" s="14">
-        <v>-9.852216748768</v>
-      </c>
-      <c r="I24" s="15">
-        <v>468</v>
-      </c>
-      <c r="J24" s="15">
-        <v>686</v>
-      </c>
-      <c r="K24" s="14">
-        <v>-31.778425655976</v>
-      </c>
-      <c r="L24" s="14">
-        <v>-19.310344827586</v>
-      </c>
-      <c r="M24" s="14">
-        <v>52.442996742671</v>
+      <c r="C24" s="14">
+        <v>67</v>
+      </c>
+      <c r="D24" s="14">
+        <v>46</v>
+      </c>
+      <c r="E24" s="15">
+        <v>45.652173913043</v>
+      </c>
+      <c r="F24" s="14">
+        <v>207</v>
+      </c>
+      <c r="G24" s="14">
+        <v>198</v>
+      </c>
+      <c r="H24" s="15">
+        <v>4.545454545454</v>
+      </c>
+      <c r="I24" s="14">
+        <v>535</v>
+      </c>
+      <c r="J24" s="14">
+        <v>732</v>
+      </c>
+      <c r="K24" s="15">
+        <v>-26.912568306010</v>
+      </c>
+      <c r="L24" s="15">
+        <v>-17.310664605873</v>
+      </c>
+      <c r="M24" s="15">
+        <v>61.631419939577</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1305,35 +1305,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>28</v>
-      </c>
-      <c r="D25" s="15">
-        <v>44</v>
-      </c>
-      <c r="E25" s="14">
-        <v>-36.363636363636</v>
-      </c>
-      <c r="F25" s="15">
-        <v>134</v>
-      </c>
-      <c r="G25" s="15">
-        <v>194</v>
-      </c>
-      <c r="H25" s="14">
-        <v>-30.927835051546</v>
-      </c>
-      <c r="I25" s="15">
-        <v>345</v>
-      </c>
-      <c r="J25" s="15">
-        <v>590</v>
-      </c>
-      <c r="K25" s="14">
-        <v>-41.525423728813</v>
-      </c>
-      <c r="L25" s="14">
-        <v>-34.659090909090</v>
+      <c r="C25" s="14">
+        <v>52</v>
+      </c>
+      <c r="D25" s="14">
+        <v>47</v>
+      </c>
+      <c r="E25" s="15">
+        <v>10.638297872340</v>
+      </c>
+      <c r="F25" s="14">
+        <v>150</v>
+      </c>
+      <c r="G25" s="14">
+        <v>195</v>
+      </c>
+      <c r="H25" s="15">
+        <v>-23.076923076923</v>
+      </c>
+      <c r="I25" s="14">
+        <v>395</v>
+      </c>
+      <c r="J25" s="14">
+        <v>637</v>
+      </c>
+      <c r="K25" s="15">
+        <v>-37.990580847723</v>
+      </c>
+      <c r="L25" s="15">
+        <v>-31.304347826087</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1346,38 +1346,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
-        <v>4</v>
-      </c>
-      <c r="D26" s="15">
+      <c r="C26" s="14">
         <v>7</v>
       </c>
-      <c r="E26" s="14">
-        <v>-42.857142857142</v>
-      </c>
-      <c r="F26" s="15">
-        <v>24</v>
-      </c>
-      <c r="G26" s="15">
-        <v>28</v>
-      </c>
-      <c r="H26" s="14">
-        <v>-14.285714285714</v>
-      </c>
-      <c r="I26" s="15">
-        <v>64</v>
-      </c>
-      <c r="J26" s="15">
-        <v>58</v>
-      </c>
-      <c r="K26" s="14">
-        <v>10.344827586206</v>
-      </c>
-      <c r="L26" s="14">
-        <v>-3.030303030303</v>
-      </c>
-      <c r="M26" s="14">
-        <v>-7.246376811594</v>
+      <c r="D26" s="14">
+        <v>5</v>
+      </c>
+      <c r="E26" s="15">
+        <v>40</v>
+      </c>
+      <c r="F26" s="14">
+        <v>27</v>
+      </c>
+      <c r="G26" s="14">
+        <v>30</v>
+      </c>
+      <c r="H26" s="15">
+        <v>-10</v>
+      </c>
+      <c r="I26" s="14">
+        <v>70</v>
+      </c>
+      <c r="J26" s="14">
+        <v>63</v>
+      </c>
+      <c r="K26" s="15">
+        <v>11.111111111111</v>
+      </c>
+      <c r="L26" s="15">
+        <v>-7.894736842105</v>
+      </c>
+      <c r="M26" s="15">
+        <v>-7.894736842105</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,31 +1390,31 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E27" s="15">
         <v>-100</v>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="14">
         <v>1</v>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="14">
         <v>2</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H27" s="15">
         <v>-50</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="14">
         <v>3</v>
       </c>
-      <c r="J27" s="15">
-        <v>5</v>
-      </c>
-      <c r="K27" s="14">
-        <v>-40</v>
-      </c>
-      <c r="L27" s="14">
+      <c r="J27" s="14">
+        <v>6</v>
+      </c>
+      <c r="K27" s="15">
+        <v>-50</v>
+      </c>
+      <c r="L27" s="15">
         <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="14">
+        <v>4</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>300</v>
+      </c>
+      <c r="F28" s="14">
+        <v>7</v>
+      </c>
+      <c r="G28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>100</v>
-      </c>
-      <c r="F28" s="15">
-        <v>4</v>
-      </c>
-      <c r="G28" s="15">
-        <v>3</v>
-      </c>
-      <c r="H28" s="14">
-        <v>33.333333333333</v>
-      </c>
-      <c r="I28" s="15">
-        <v>8</v>
-      </c>
-      <c r="J28" s="15">
-        <v>16</v>
-      </c>
-      <c r="K28" s="14">
-        <v>-50</v>
-      </c>
-      <c r="L28" s="14">
-        <v>-68</v>
+      <c r="H28" s="15">
+        <v>250</v>
+      </c>
+      <c r="I28" s="14">
+        <v>12</v>
+      </c>
+      <c r="J28" s="14">
+        <v>17</v>
+      </c>
+      <c r="K28" s="15">
+        <v>-29.411764705882</v>
+      </c>
+      <c r="L28" s="15">
+        <v>-60</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1496,13 +1496,13 @@
       <c r="K29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L29" s="14">
+      <c r="L29" s="15">
         <v>-100</v>
       </c>
-      <c r="M29" s="14">
+      <c r="M29" s="15">
         <v>-100</v>
       </c>
-      <c r="N29" s="14">
+      <c r="N29" s="15">
         <v>-100</v>
       </c>
     </row>
@@ -1537,13 +1537,13 @@
       <c r="K30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L30" s="14">
+      <c r="L30" s="15">
         <v>-100</v>
       </c>
-      <c r="M30" s="14">
+      <c r="M30" s="15">
         <v>-100</v>
       </c>
-      <c r="N30" s="14">
+      <c r="N30" s="15">
         <v>-100</v>
       </c>
     </row>
@@ -1554,32 +1554,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="15">
-        <v>1</v>
-      </c>
-      <c r="H31" s="14">
+      <c r="G31" s="14">
+        <v>2</v>
+      </c>
+      <c r="H31" s="15">
         <v>-100</v>
       </c>
-      <c r="I31" s="15">
+      <c r="I31" s="14">
         <v>2</v>
       </c>
-      <c r="J31" s="15">
-        <v>3</v>
-      </c>
-      <c r="K31" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="L31" s="14">
-        <v>-60</v>
+      <c r="J31" s="14">
+        <v>4</v>
+      </c>
+      <c r="K31" s="15">
+        <v>-50</v>
+      </c>
+      <c r="L31" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,8 +1610,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1619,8 +1619,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1628,14 +1628,14 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J33" s="15">
+      <c r="I33" s="14">
+        <v>1</v>
+      </c>
+      <c r="J33" s="14">
         <v>2</v>
       </c>
-      <c r="K33" s="14">
-        <v>-100</v>
+      <c r="K33" s="15">
+        <v>-50</v>
       </c>
       <c r="L33" s="13" t="s">
         <v>21</v>
@@ -1745,16 +1745,16 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>9</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>5</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="14">
         <v>6</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="14">
         <v>1</v>
       </c>
       <c r="K39" s="13" t="s">
@@ -1774,31 +1774,31 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="14">
         <v>27</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="14">
         <v>30</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="14">
         <v>17</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="14">
         <v>9</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <v>13</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="15">
         <v>44.444444444444</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="15">
         <v>-23.529411764705</v>
       </c>
-      <c r="M40" s="14">
+      <c r="M40" s="15">
         <v>-56.666666666666</v>
       </c>
-      <c r="N40" s="14">
+      <c r="N40" s="15">
         <v>-51.851851851851</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>1904</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>1378</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>459</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <v>359</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <v>165</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="15">
         <v>-54.038997214484</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="15">
         <v>-64.052287581699</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="15">
         <v>-88.026124818577</v>
       </c>
-      <c r="N41" s="14">
+      <c r="N41" s="15">
         <v>-91.334033613445</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>312</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>295</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>185</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="14">
         <v>127</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>208</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="15">
         <v>63.779527559055</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="15">
         <v>12.432432432432</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="15">
         <v>-29.491525423728</v>
       </c>
-      <c r="N42" s="14">
+      <c r="N42" s="15">
         <v>-33.333333333333</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <v>3695</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>3019</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>1028</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <v>701</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>275</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="15">
         <v>-60.770328102710</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="15">
         <v>-73.249027237354</v>
       </c>
-      <c r="M43" s="14">
+      <c r="M43" s="15">
         <v>-90.891023517721</v>
       </c>
-      <c r="N43" s="14">
+      <c r="N43" s="15">
         <v>-92.557510148849</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>5406</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>3792</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>2167</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <v>2208</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>1596</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="15">
         <v>-27.717391304347</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="15">
         <v>-26.349792339640</v>
       </c>
-      <c r="M44" s="14">
+      <c r="M44" s="15">
         <v>-57.911392405063</v>
       </c>
-      <c r="N44" s="14">
+      <c r="N44" s="15">
         <v>-70.477247502774</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>3338</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>3457</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>997</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <v>320</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <v>60</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="15">
         <v>-81.25</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="15">
         <v>-93.981945837512</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="15">
         <v>-98.264391090540</v>
       </c>
-      <c r="N45" s="14">
+      <c r="N45" s="15">
         <v>-98.202516476932</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-019pct.xlsx
+++ b/data/source/weekly/cs-en-us-019pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -914,13 +914,13 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
         <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H16" s="15">
-        <v>-23.529411764705</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I16" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J16" s="14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K16" s="15">
-        <v>-40</v>
+        <v>-40.476190476190</v>
       </c>
       <c r="L16" s="15">
-        <v>-45.454545454545</v>
+        <v>-46.808510638297</v>
       </c>
       <c r="M16" s="15">
-        <v>-14.285714285714</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.808873720136</v>
+        <v>-92.138364779874</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>2</v>
+      </c>
+      <c r="D17" s="14">
         <v>4</v>
       </c>
-      <c r="D17" s="14">
-        <v>3</v>
-      </c>
       <c r="E17" s="15">
-        <v>33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="14">
         <v>18</v>
       </c>
       <c r="G17" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>5.882352941176</v>
       </c>
       <c r="I17" s="14">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J17" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K17" s="15">
-        <v>13.157894736842</v>
+        <v>11.904761904761</v>
       </c>
       <c r="L17" s="15">
-        <v>53.571428571428</v>
+        <v>42.424242424242</v>
       </c>
       <c r="M17" s="15">
-        <v>95.454545454545</v>
+        <v>113.636363636364</v>
       </c>
       <c r="N17" s="15">
-        <v>-15.686274509803</v>
+        <v>-18.965517241379</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-62.5</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H18" s="15">
-        <v>-27.777777777777</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="I18" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J18" s="14">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K18" s="15">
-        <v>-45.454545454545</v>
+        <v>-45.714285714285</v>
       </c>
       <c r="L18" s="15">
-        <v>-36.842105263157</v>
+        <v>-39.682539682539</v>
       </c>
       <c r="M18" s="15">
-        <v>-52.631578947368</v>
+        <v>-54.216867469879</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.939393939393</v>
+        <v>-94.099378881987</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,48 +1060,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D19" s="14">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="E19" s="15">
-        <v>-32.5</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G19" s="14">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H19" s="15">
-        <v>-16.541353383458</v>
+        <v>-16.40625</v>
       </c>
       <c r="I19" s="14">
-        <v>312</v>
+        <v>338</v>
       </c>
       <c r="J19" s="14">
-        <v>323</v>
+        <v>349</v>
       </c>
       <c r="K19" s="15">
-        <v>-3.405572755417</v>
+        <v>-3.151862464183</v>
       </c>
       <c r="L19" s="15">
-        <v>-12.112676056338</v>
+        <v>-10.817941952506</v>
       </c>
       <c r="M19" s="15">
-        <v>15.985130111524</v>
+        <v>19.858156028368</v>
       </c>
       <c r="N19" s="15">
-        <v>-62.043795620438</v>
+        <v>-61.979752530933</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1113,10 +1113,10 @@
         <v>6</v>
       </c>
       <c r="G20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I20" s="14">
         <v>14</v>
@@ -1128,13 +1128,13 @@
         <v>16.666666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>7.692307692307</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="M20" s="15">
         <v>100</v>
       </c>
       <c r="N20" s="15">
-        <v>-98.202824133504</v>
+        <v>-98.366394399066</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D21" s="17">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="E21" s="18">
-        <v>-29.090909090909</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F21" s="17">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="G21" s="17">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="H21" s="18">
-        <v>-14.210526315789</v>
+        <v>-12.849162011173</v>
       </c>
       <c r="I21" s="17">
-        <v>433</v>
+        <v>467</v>
       </c>
       <c r="J21" s="17">
-        <v>483</v>
+        <v>519</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.351966873706</v>
+        <v>-10.019267822736</v>
       </c>
       <c r="L21" s="18">
-        <v>-13.572854291417</v>
+        <v>-13.837638376383</v>
       </c>
       <c r="M21" s="18">
-        <v>6.650246305418</v>
+        <v>8.857808857808</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.986247544204</v>
+        <v>-83.152958152958</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1192,28 +1192,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" s="14">
         <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I22" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J22" s="14">
         <v>11</v>
       </c>
       <c r="K22" s="15">
-        <v>-18.181818181818</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L22" s="15">
-        <v>-10</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M22" s="15">
-        <v>350</v>
+        <v>233.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1233,28 +1233,28 @@
         <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="14">
         <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="I23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K23" s="15">
-        <v>-55.555555555555</v>
+        <v>-50</v>
       </c>
       <c r="L23" s="15">
-        <v>-42.857142857142</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M23" s="15">
-        <v>-50</v>
+        <v>-37.5</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="D24" s="14">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="E24" s="15">
-        <v>45.652173913043</v>
+        <v>-42.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="G24" s="14">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="H24" s="15">
-        <v>4.545454545454</v>
+        <v>-14.347826086956</v>
       </c>
       <c r="I24" s="14">
-        <v>535</v>
+        <v>578</v>
       </c>
       <c r="J24" s="14">
-        <v>732</v>
+        <v>807</v>
       </c>
       <c r="K24" s="15">
-        <v>-26.912568306010</v>
+        <v>-28.376703841387</v>
       </c>
       <c r="L24" s="15">
-        <v>-17.310664605873</v>
+        <v>-18.476727785613</v>
       </c>
       <c r="M24" s="15">
-        <v>61.631419939577</v>
+        <v>63.739376770538</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="D25" s="14">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="E25" s="15">
-        <v>10.638297872340</v>
+        <v>-47.692307692307</v>
       </c>
       <c r="F25" s="14">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="G25" s="14">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="H25" s="15">
-        <v>-23.076923076923</v>
+        <v>-34.259259259259</v>
       </c>
       <c r="I25" s="14">
-        <v>395</v>
+        <v>430</v>
       </c>
       <c r="J25" s="14">
-        <v>637</v>
+        <v>702</v>
       </c>
       <c r="K25" s="15">
-        <v>-37.990580847723</v>
+        <v>-38.746438746438</v>
       </c>
       <c r="L25" s="15">
-        <v>-31.304347826087</v>
+        <v>-31.528662420382</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E26" s="15">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="F26" s="14">
         <v>27</v>
       </c>
       <c r="G26" s="14">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H26" s="15">
-        <v>-10</v>
+        <v>17.391304347826</v>
       </c>
       <c r="I26" s="14">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J26" s="14">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K26" s="15">
-        <v>11.111111111111</v>
+        <v>17.1875</v>
       </c>
       <c r="L26" s="15">
-        <v>-7.894736842105</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="M26" s="15">
-        <v>-7.894736842105</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,14 +1387,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="14">
+      <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
@@ -1406,13 +1406,13 @@
         <v>-50</v>
       </c>
       <c r="I27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="14">
         <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L27" s="15">
         <v>0</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>3</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>50</v>
+      </c>
+      <c r="F28" s="14">
+        <v>10</v>
+      </c>
+      <c r="G28" s="14">
         <v>4</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>300</v>
-      </c>
-      <c r="F28" s="14">
-        <v>7</v>
-      </c>
-      <c r="G28" s="14">
-        <v>2</v>
-      </c>
       <c r="H28" s="15">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="I28" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J28" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K28" s="15">
-        <v>-29.411764705882</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="L28" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1554,17 +1554,17 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="14">
         <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" s="14">
-        <v>2</v>
       </c>
       <c r="H31" s="15">
         <v>-100</v>
@@ -1579,7 +1579,7 @@
         <v>-50</v>
       </c>
       <c r="L31" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,8 +1610,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-019pct.xlsx
+++ b/data/source/weekly/cs-en-us-019pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -863,8 +863,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -940,37 +940,37 @@
         <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>-80</v>
       </c>
       <c r="F16" s="14">
         <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>-7.142857142857</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J16" s="14">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K16" s="15">
-        <v>-40.476190476190</v>
+        <v>-42.553191489361</v>
       </c>
       <c r="L16" s="15">
-        <v>-46.808510638297</v>
+        <v>-46</v>
       </c>
       <c r="M16" s="15">
-        <v>-16.666666666666</v>
+        <v>-15.625</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.138364779874</v>
+        <v>-92.219020172910</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -981,37 +981,37 @@
         <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G17" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H17" s="15">
-        <v>5.882352941176</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I17" s="14">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J17" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K17" s="15">
-        <v>11.904761904761</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L17" s="15">
-        <v>42.424242424242</v>
+        <v>31.578947368421</v>
       </c>
       <c r="M17" s="15">
-        <v>113.636363636364</v>
+        <v>108.333333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>-18.965517241379</v>
+        <v>-30.555555555555</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G18" s="14">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H18" s="15">
-        <v>-41.176470588235</v>
+        <v>-52</v>
       </c>
       <c r="I18" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J18" s="14">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="K18" s="15">
-        <v>-45.714285714285</v>
+        <v>-45.569620253164</v>
       </c>
       <c r="L18" s="15">
-        <v>-39.682539682539</v>
+        <v>-36.764705882352</v>
       </c>
       <c r="M18" s="15">
-        <v>-54.216867469879</v>
+        <v>-49.411764705882</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.099378881987</v>
+        <v>-93.812949640287</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,48 +1060,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D19" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-29.629629629629</v>
       </c>
       <c r="F19" s="14">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="G19" s="14">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="H19" s="15">
-        <v>-16.40625</v>
+        <v>-26.829268292682</v>
       </c>
       <c r="I19" s="14">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="J19" s="14">
-        <v>349</v>
+        <v>376</v>
       </c>
       <c r="K19" s="15">
-        <v>-3.151862464183</v>
+        <v>-5.053191489361</v>
       </c>
       <c r="L19" s="15">
-        <v>-10.817941952506</v>
+        <v>-12.926829268292</v>
       </c>
       <c r="M19" s="15">
-        <v>19.858156028368</v>
+        <v>19.397993311036</v>
       </c>
       <c r="N19" s="15">
-        <v>-61.979752530933</v>
+        <v>-62.928348909657</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1119,22 +1119,22 @@
         <v>100</v>
       </c>
       <c r="I20" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J20" s="14">
         <v>12</v>
       </c>
       <c r="K20" s="15">
-        <v>16.666666666666</v>
+        <v>25</v>
       </c>
       <c r="L20" s="15">
-        <v>-6.666666666666</v>
+        <v>0</v>
       </c>
       <c r="M20" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-98.366394399066</v>
+        <v>-98.362445414847</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,48 +1142,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D21" s="17">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E21" s="18">
-        <v>-11.111111111111</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F21" s="17">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="G21" s="17">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H21" s="18">
-        <v>-12.849162011173</v>
+        <v>-24.858757062146</v>
       </c>
       <c r="I21" s="17">
-        <v>467</v>
+        <v>497</v>
       </c>
       <c r="J21" s="17">
-        <v>519</v>
+        <v>563</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.019267822736</v>
+        <v>-11.722912966252</v>
       </c>
       <c r="L21" s="18">
-        <v>-13.837638376383</v>
+        <v>-15.187713310580</v>
       </c>
       <c r="M21" s="18">
-        <v>8.857808857808</v>
+        <v>9.471365638766</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.152958152958</v>
+        <v>-83.427809269756</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>2</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1192,28 +1192,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>66.666666666666</v>
+        <v>200</v>
       </c>
       <c r="I22" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J22" s="14">
         <v>11</v>
       </c>
       <c r="K22" s="15">
-        <v>-9.090909090909</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L22" s="15">
-        <v>-9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>233.333333333333</v>
+        <v>300</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,23 +1223,23 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
-      </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>0</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
         <v>2</v>
       </c>
       <c r="G23" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="14">
         <v>5</v>
@@ -1251,7 +1251,7 @@
         <v>-50</v>
       </c>
       <c r="L23" s="15">
-        <v>-28.571428571428</v>
+        <v>-37.5</v>
       </c>
       <c r="M23" s="15">
         <v>-37.5</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D24" s="14">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E24" s="15">
-        <v>-42.666666666666</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="F24" s="14">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G24" s="14">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="H24" s="15">
-        <v>-14.347826086956</v>
+        <v>-16.317991631799</v>
       </c>
       <c r="I24" s="14">
-        <v>578</v>
+        <v>619</v>
       </c>
       <c r="J24" s="14">
-        <v>807</v>
+        <v>870</v>
       </c>
       <c r="K24" s="15">
-        <v>-28.376703841387</v>
+        <v>-28.850574712643</v>
       </c>
       <c r="L24" s="15">
-        <v>-18.476727785613</v>
+        <v>-18.445322793148</v>
       </c>
       <c r="M24" s="15">
-        <v>63.739376770538</v>
+        <v>56.313131313131</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D25" s="14">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="E25" s="15">
-        <v>-47.692307692307</v>
+        <v>-39.534883720930</v>
       </c>
       <c r="F25" s="14">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G25" s="14">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="H25" s="15">
-        <v>-34.259259259259</v>
+        <v>-30.150753768844</v>
       </c>
       <c r="I25" s="14">
-        <v>430</v>
+        <v>457</v>
       </c>
       <c r="J25" s="14">
-        <v>702</v>
+        <v>745</v>
       </c>
       <c r="K25" s="15">
-        <v>-38.746438746438</v>
+        <v>-38.657718120805</v>
       </c>
       <c r="L25" s="15">
-        <v>-31.528662420382</v>
+        <v>-31.689088191330</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="F26" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G26" s="14">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H26" s="15">
-        <v>17.391304347826</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="J26" s="14">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="K26" s="15">
-        <v>17.1875</v>
+        <v>20.289855072463</v>
       </c>
       <c r="L26" s="15">
-        <v>-7.407407407407</v>
+        <v>-7.777777777777</v>
       </c>
       <c r="M26" s="15">
-        <v>-7.407407407407</v>
+        <v>-1.190476190476</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E28" s="15">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>150</v>
+        <v>37.5</v>
       </c>
       <c r="I28" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J28" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K28" s="15">
-        <v>-21.052631578947</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="L28" s="15">
-        <v>-50</v>
+        <v>-45.161290322580</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,35 +1551,35 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
+      </c>
+      <c r="D31" s="14">
+        <v>3</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H31" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="I31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K31" s="15">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L31" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1637,8 +1637,8 @@
       <c r="K33" s="15">
         <v>-50</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="15">
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-019pct.xlsx
+++ b/data/source/weekly/cs-en-us-019pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -888,15 +888,15 @@
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,7 +905,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -914,22 +914,22 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L15" s="15">
         <v>0</v>
       </c>
       <c r="M15" s="15">
+        <v>25</v>
+      </c>
+      <c r="N15" s="15">
         <v>0</v>
-      </c>
-      <c r="N15" s="15">
-        <v>-20</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>8.333333333333</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J16" s="14">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K16" s="15">
-        <v>-42.553191489361</v>
+        <v>-39.215686274509</v>
       </c>
       <c r="L16" s="15">
-        <v>-46</v>
+        <v>-41.509433962264</v>
       </c>
       <c r="M16" s="15">
-        <v>-15.625</v>
+        <v>-16.216216216216</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.219020172910</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>3</v>
+      </c>
+      <c r="D17" s="14">
         <v>2</v>
       </c>
-      <c r="D17" s="14">
-        <v>3</v>
-      </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G17" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H17" s="15">
-        <v>-21.428571428571</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J17" s="14">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K17" s="15">
-        <v>11.111111111111</v>
+        <v>14.893617021276</v>
       </c>
       <c r="L17" s="15">
-        <v>31.578947368421</v>
+        <v>35</v>
       </c>
       <c r="M17" s="15">
-        <v>108.333333333333</v>
+        <v>107.692307692308</v>
       </c>
       <c r="N17" s="15">
-        <v>-30.555555555555</v>
+        <v>-31.645569620253</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D18" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>-44.444444444444</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G18" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H18" s="15">
-        <v>-52</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="J18" s="14">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="K18" s="15">
-        <v>-45.569620253164</v>
+        <v>-40</v>
       </c>
       <c r="L18" s="15">
-        <v>-36.764705882352</v>
+        <v>-27.142857142857</v>
       </c>
       <c r="M18" s="15">
-        <v>-49.411764705882</v>
+        <v>-41.379310344827</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.812949640287</v>
+        <v>-93.245033112582</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D19" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E19" s="15">
-        <v>-29.629629629629</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="F19" s="14">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G19" s="14">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H19" s="15">
-        <v>-26.829268292682</v>
+        <v>-19.834710743801</v>
       </c>
       <c r="I19" s="14">
-        <v>357</v>
+        <v>382</v>
       </c>
       <c r="J19" s="14">
-        <v>376</v>
+        <v>404</v>
       </c>
       <c r="K19" s="15">
-        <v>-5.053191489361</v>
+        <v>-5.445544554455</v>
       </c>
       <c r="L19" s="15">
-        <v>-12.926829268292</v>
+        <v>-9.905660377358</v>
       </c>
       <c r="M19" s="15">
-        <v>19.397993311036</v>
+        <v>16.819571865443</v>
       </c>
       <c r="N19" s="15">
-        <v>-62.928348909657</v>
+        <v>-63.304514889529</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1103,38 +1103,38 @@
       <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H20" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I20" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J20" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K20" s="15">
-        <v>25</v>
+        <v>23.076923076923</v>
       </c>
       <c r="L20" s="15">
-        <v>0</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="M20" s="15">
-        <v>66.666666666666</v>
+        <v>45.454545454545</v>
       </c>
       <c r="N20" s="15">
-        <v>-98.362445414847</v>
+        <v>-98.372329603255</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D21" s="17">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E21" s="18">
-        <v>-36.363636363636</v>
+        <v>-4.878048780487</v>
       </c>
       <c r="F21" s="17">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="G21" s="17">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H21" s="18">
-        <v>-24.858757062146</v>
+        <v>-17.613636363636</v>
       </c>
       <c r="I21" s="17">
-        <v>497</v>
+        <v>540</v>
       </c>
       <c r="J21" s="17">
-        <v>563</v>
+        <v>604</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.722912966252</v>
+        <v>-10.596026490066</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.187713310580</v>
+        <v>-11.475409836065</v>
       </c>
       <c r="M21" s="18">
-        <v>9.471365638766</v>
+        <v>9.533468559837</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.427809269756</v>
+        <v>-83.323038912909</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1192,28 +1192,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
-      </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <v>200</v>
+        <v>4</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J22" s="14">
         <v>11</v>
       </c>
       <c r="K22" s="15">
-        <v>9.090909090909</v>
+        <v>27.272727272727</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,38 +1223,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="C23" s="14">
+        <v>1</v>
+      </c>
+      <c r="D23" s="14">
+        <v>2</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="14">
         <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="I23" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J23" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K23" s="15">
         <v>-50</v>
       </c>
       <c r="L23" s="15">
-        <v>-37.5</v>
+        <v>-25</v>
       </c>
       <c r="M23" s="15">
-        <v>-37.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D24" s="14">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E24" s="15">
-        <v>-38.095238095238</v>
+        <v>-45</v>
       </c>
       <c r="F24" s="14">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="G24" s="14">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="H24" s="15">
-        <v>-16.317991631799</v>
+        <v>-25.819672131147</v>
       </c>
       <c r="I24" s="14">
-        <v>619</v>
+        <v>650</v>
       </c>
       <c r="J24" s="14">
-        <v>870</v>
+        <v>930</v>
       </c>
       <c r="K24" s="15">
-        <v>-28.850574712643</v>
+        <v>-30.107526881720</v>
       </c>
       <c r="L24" s="15">
-        <v>-18.445322793148</v>
+        <v>-19.254658385093</v>
       </c>
       <c r="M24" s="15">
-        <v>56.313131313131</v>
+        <v>56.25</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D25" s="14">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E25" s="15">
-        <v>-39.534883720930</v>
+        <v>-60.377358490566</v>
       </c>
       <c r="F25" s="14">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G25" s="14">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="H25" s="15">
-        <v>-30.150753768844</v>
+        <v>-36.057692307692</v>
       </c>
       <c r="I25" s="14">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="J25" s="14">
-        <v>745</v>
+        <v>798</v>
       </c>
       <c r="K25" s="15">
-        <v>-38.657718120805</v>
+        <v>-40.350877192982</v>
       </c>
       <c r="L25" s="15">
-        <v>-31.689088191330</v>
+        <v>-32.768361581920</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E26" s="15">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="F26" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G26" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H26" s="15">
-        <v>33.333333333333</v>
+        <v>80</v>
       </c>
       <c r="I26" s="14">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="J26" s="14">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K26" s="15">
-        <v>20.289855072463</v>
+        <v>23.287671232876</v>
       </c>
       <c r="L26" s="15">
-        <v>-7.777777777777</v>
+        <v>-4.255319148936</v>
       </c>
       <c r="M26" s="15">
-        <v>-1.190476190476</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,22 +1397,22 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
+        <v>2</v>
+      </c>
+      <c r="G27" s="14">
         <v>1</v>
       </c>
-      <c r="G27" s="14">
-        <v>2</v>
-      </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="14">
         <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L27" s="15">
         <v>0</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="14">
-        <v>4</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-50</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>37.5</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I28" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J28" s="14">
         <v>23</v>
       </c>
       <c r="K28" s="15">
-        <v>-26.086956521739</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="L28" s="15">
-        <v>-45.161290322580</v>
+        <v>-51.351351351351</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,8 +1469,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1478,8 +1478,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1487,8 +1487,8 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="14">
+        <v>1</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1497,21 +1497,21 @@
         <v>21</v>
       </c>
       <c r="L29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="N29" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1519,8 +1519,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1528,8 +1528,8 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="14">
+        <v>1</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1538,27 +1538,27 @@
         <v>21</v>
       </c>
       <c r="L30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
-      </c>
-      <c r="D31" s="14">
-        <v>3</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-66.666666666666</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-019pct.xlsx
+++ b/data/source/weekly/cs-en-us-019pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -905,7 +905,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -914,22 +914,22 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M15" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F16" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H16" s="15">
-        <v>-26.666666666666</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I16" s="14">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J16" s="14">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K16" s="15">
-        <v>-39.215686274509</v>
+        <v>-32.075471698113</v>
       </c>
       <c r="L16" s="15">
-        <v>-41.509433962264</v>
+        <v>-38.983050847457</v>
       </c>
       <c r="M16" s="15">
-        <v>-16.216216216216</v>
+        <v>-12.195121951219</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.666666666666</v>
+        <v>-90.977443609022</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>50</v>
+        <v>-60</v>
       </c>
       <c r="F17" s="14">
+        <v>11</v>
+      </c>
+      <c r="G17" s="14">
         <v>14</v>
       </c>
-      <c r="G17" s="14">
-        <v>12</v>
-      </c>
       <c r="H17" s="15">
-        <v>16.666666666666</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I17" s="14">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J17" s="14">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K17" s="15">
-        <v>14.893617021276</v>
+        <v>7.692307692307</v>
       </c>
       <c r="L17" s="15">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M17" s="15">
-        <v>107.692307692308</v>
+        <v>100</v>
       </c>
       <c r="N17" s="15">
-        <v>-31.645569620253</v>
+        <v>-35.632183908046</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>16.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
         <v>18</v>
       </c>
       <c r="G18" s="14">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H18" s="15">
-        <v>-33.333333333333</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="I18" s="14">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J18" s="14">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K18" s="15">
+        <v>-39.325842696629</v>
+      </c>
+      <c r="L18" s="15">
+        <v>-26.027397260274</v>
+      </c>
+      <c r="M18" s="15">
         <v>-40</v>
       </c>
-      <c r="L18" s="15">
-        <v>-27.142857142857</v>
-      </c>
-      <c r="M18" s="15">
-        <v>-41.379310344827</v>
-      </c>
       <c r="N18" s="15">
-        <v>-93.245033112582</v>
+        <v>-93.374233128834</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,81 +1060,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D19" s="14">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E19" s="15">
-        <v>-17.857142857142</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F19" s="14">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G19" s="14">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H19" s="15">
-        <v>-19.834710743801</v>
+        <v>-18.253968253968</v>
       </c>
       <c r="I19" s="14">
-        <v>382</v>
+        <v>416</v>
       </c>
       <c r="J19" s="14">
-        <v>404</v>
+        <v>449</v>
       </c>
       <c r="K19" s="15">
-        <v>-5.445544554455</v>
+        <v>-7.349665924276</v>
       </c>
       <c r="L19" s="15">
-        <v>-9.905660377358</v>
+        <v>-8.370044052863</v>
       </c>
       <c r="M19" s="15">
-        <v>16.819571865443</v>
+        <v>16.526610644257</v>
       </c>
       <c r="N19" s="15">
-        <v>-63.304514889529</v>
+        <v>-62.989323843416</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
       </c>
       <c r="E20" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="14">
+        <v>2</v>
+      </c>
+      <c r="G20" s="14">
+        <v>2</v>
+      </c>
+      <c r="H20" s="15">
         <v>0</v>
-      </c>
-      <c r="F20" s="14">
-        <v>3</v>
-      </c>
-      <c r="G20" s="14">
-        <v>1</v>
-      </c>
-      <c r="H20" s="15">
-        <v>200</v>
       </c>
       <c r="I20" s="14">
         <v>16</v>
       </c>
       <c r="J20" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K20" s="15">
-        <v>23.076923076923</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L20" s="15">
-        <v>-5.882352941176</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="M20" s="15">
-        <v>45.454545454545</v>
+        <v>6.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-98.372329603255</v>
+        <v>-98.480531813865</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D21" s="17">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E21" s="18">
-        <v>-4.878048780487</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="F21" s="17">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G21" s="17">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H21" s="18">
-        <v>-17.613636363636</v>
+        <v>-16.292134831460</v>
       </c>
       <c r="I21" s="17">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="J21" s="17">
-        <v>604</v>
+        <v>661</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.596026490066</v>
+        <v>-11.497730711043</v>
       </c>
       <c r="L21" s="18">
-        <v>-11.475409836065</v>
+        <v>-10.138248847926</v>
       </c>
       <c r="M21" s="18">
-        <v>9.533468559837</v>
+        <v>9.141791044776</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.323038912909</v>
+        <v>-83.218588640275</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,7 +1183,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1192,7 +1192,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1201,19 +1201,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J22" s="14">
         <v>11</v>
       </c>
       <c r="K22" s="15">
-        <v>27.272727272727</v>
+        <v>36.363636363636</v>
       </c>
       <c r="L22" s="15">
-        <v>16.666666666666</v>
+        <v>25</v>
       </c>
       <c r="M22" s="15">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,38 +1223,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="14">
+      <c r="E23" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F23" s="14">
         <v>2</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F23" s="14">
-        <v>3</v>
       </c>
       <c r="G23" s="14">
         <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="14">
         <v>6</v>
       </c>
       <c r="J23" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K23" s="15">
-        <v>-50</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="L23" s="15">
         <v>-25</v>
       </c>
       <c r="M23" s="15">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D24" s="14">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E24" s="15">
-        <v>-45</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="F24" s="14">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="G24" s="14">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="H24" s="15">
-        <v>-25.819672131147</v>
+        <v>-34.4</v>
       </c>
       <c r="I24" s="14">
-        <v>650</v>
+        <v>699</v>
       </c>
       <c r="J24" s="14">
-        <v>930</v>
+        <v>982</v>
       </c>
       <c r="K24" s="15">
-        <v>-30.107526881720</v>
+        <v>-28.818737270875</v>
       </c>
       <c r="L24" s="15">
-        <v>-19.254658385093</v>
+        <v>-18.531468531468</v>
       </c>
       <c r="M24" s="15">
-        <v>56.25</v>
+        <v>58.144796380090</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D25" s="14">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E25" s="15">
-        <v>-60.377358490566</v>
+        <v>-21.951219512195</v>
       </c>
       <c r="F25" s="14">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="G25" s="14">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="H25" s="15">
-        <v>-36.057692307692</v>
+        <v>-44.554455445544</v>
       </c>
       <c r="I25" s="14">
-        <v>476</v>
+        <v>508</v>
       </c>
       <c r="J25" s="14">
-        <v>798</v>
+        <v>839</v>
       </c>
       <c r="K25" s="15">
-        <v>-40.350877192982</v>
+        <v>-39.451728247914</v>
       </c>
       <c r="L25" s="15">
-        <v>-32.768361581920</v>
+        <v>-32.981530343007</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D26" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G26" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H26" s="15">
-        <v>80</v>
+        <v>26.315789473684</v>
       </c>
       <c r="I26" s="14">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="J26" s="14">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K26" s="15">
-        <v>23.287671232876</v>
+        <v>13.414634146341</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.255319148936</v>
+        <v>-7</v>
       </c>
       <c r="M26" s="15">
-        <v>-5.263157894736</v>
+        <v>-7.920792079207</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,32 +1390,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>-16.666666666666</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,7 +1429,7 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1438,25 +1438,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>42.857142857142</v>
+        <v>50</v>
       </c>
       <c r="I28" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J28" s="14">
         <v>23</v>
       </c>
       <c r="K28" s="15">
-        <v>-21.739130434782</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="L28" s="15">
-        <v>-51.351351351351</v>
+        <v>-47.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,8 +1469,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1510,8 +1510,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1564,10 +1564,10 @@
         <v>1</v>
       </c>
       <c r="G31" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H31" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>
@@ -1579,7 +1579,7 @@
         <v>-57.142857142857</v>
       </c>
       <c r="L31" s="15">
-        <v>-66.666666666666</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1619,8 +1619,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="14">
-        <v>1</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-019pct.xlsx
+++ b/data/source/weekly/cs-en-us-019pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,7 +905,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>150</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
         <v>12</v>
       </c>
       <c r="G16" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>-7.692307692307</v>
+        <v>-20</v>
       </c>
       <c r="I16" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J16" s="14">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K16" s="15">
-        <v>-32.075471698113</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>-38.983050847457</v>
+        <v>-37.704918032786</v>
       </c>
       <c r="M16" s="15">
-        <v>-12.195121951219</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.977443609022</v>
+        <v>-91.343963553530</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G17" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H17" s="15">
-        <v>-21.428571428571</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="I17" s="14">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="J17" s="14">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K17" s="15">
-        <v>7.692307692307</v>
+        <v>6.779661016949</v>
       </c>
       <c r="L17" s="15">
-        <v>40</v>
+        <v>34.042553191489</v>
       </c>
       <c r="M17" s="15">
-        <v>100</v>
+        <v>117.241379310345</v>
       </c>
       <c r="N17" s="15">
-        <v>-35.632183908046</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-93.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G18" s="14">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="H18" s="15">
-        <v>-21.739130434782</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="I18" s="14">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J18" s="14">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="K18" s="15">
-        <v>-39.325842696629</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="L18" s="15">
-        <v>-26.027397260274</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M18" s="15">
-        <v>-40</v>
+        <v>-39.784946236559</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.374233128834</v>
+        <v>-93.614595210946</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D19" s="14">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="E19" s="15">
-        <v>-22.222222222222</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="F19" s="14">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G19" s="14">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="H19" s="15">
-        <v>-18.253968253968</v>
+        <v>-19.402985074626</v>
       </c>
       <c r="I19" s="14">
-        <v>416</v>
+        <v>445</v>
       </c>
       <c r="J19" s="14">
-        <v>449</v>
+        <v>483</v>
       </c>
       <c r="K19" s="15">
-        <v>-7.349665924276</v>
+        <v>-7.867494824016</v>
       </c>
       <c r="L19" s="15">
-        <v>-8.370044052863</v>
+        <v>-7.098121085594</v>
       </c>
       <c r="M19" s="15">
-        <v>16.526610644257</v>
+        <v>16.187989556135</v>
       </c>
       <c r="N19" s="15">
-        <v>-62.989323843416</v>
+        <v>-62.636439966414</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1113,28 +1113,28 @@
         <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="14">
         <v>16</v>
       </c>
       <c r="J20" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K20" s="15">
-        <v>14.285714285714</v>
+        <v>6.666666666666</v>
       </c>
       <c r="L20" s="15">
         <v>-15.789473684210</v>
       </c>
       <c r="M20" s="15">
-        <v>6.666666666666</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="N20" s="15">
-        <v>-98.480531813865</v>
+        <v>-98.584070796460</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,48 +1142,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D21" s="17">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E21" s="18">
-        <v>-21.052631578947</v>
+        <v>-31.147540983606</v>
       </c>
       <c r="F21" s="17">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="G21" s="17">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="H21" s="18">
-        <v>-16.292134831460</v>
+        <v>-23.645320197044</v>
       </c>
       <c r="I21" s="17">
-        <v>585</v>
+        <v>625</v>
       </c>
       <c r="J21" s="17">
-        <v>661</v>
+        <v>722</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.497730711043</v>
+        <v>-13.434903047091</v>
       </c>
       <c r="L21" s="18">
-        <v>-10.138248847926</v>
+        <v>-9.288824383164</v>
       </c>
       <c r="M21" s="18">
-        <v>9.141791044776</v>
+        <v>9.457092819614</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.218588640275</v>
+        <v>-83.266398929049</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1192,7 +1192,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1201,19 +1201,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J22" s="14">
         <v>11</v>
       </c>
       <c r="K22" s="15">
-        <v>36.363636363636</v>
+        <v>27.272727272727</v>
       </c>
       <c r="L22" s="15">
-        <v>25</v>
+        <v>7.692307692307</v>
       </c>
       <c r="M22" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1226,20 +1226,20 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="14">
         <v>1</v>
       </c>
-      <c r="E23" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F23" s="14">
-        <v>2</v>
-      </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I23" s="14">
         <v>6</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D24" s="14">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E24" s="15">
-        <v>-3.846153846153</v>
+        <v>76.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="G24" s="14">
-        <v>250</v>
+        <v>205</v>
       </c>
       <c r="H24" s="15">
-        <v>-34.4</v>
+        <v>-16.585365853658</v>
       </c>
       <c r="I24" s="14">
-        <v>699</v>
+        <v>750</v>
       </c>
       <c r="J24" s="14">
-        <v>982</v>
+        <v>1012</v>
       </c>
       <c r="K24" s="15">
-        <v>-28.818737270875</v>
+        <v>-25.889328063241</v>
       </c>
       <c r="L24" s="15">
-        <v>-18.531468531468</v>
+        <v>-17.218543046357</v>
       </c>
       <c r="M24" s="15">
-        <v>58.144796380090</v>
+        <v>55.925155925155</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D25" s="14">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E25" s="15">
-        <v>-21.951219512195</v>
+        <v>54.838709677419</v>
       </c>
       <c r="F25" s="14">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="G25" s="14">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="H25" s="15">
-        <v>-44.554455445544</v>
+        <v>-25.595238095238</v>
       </c>
       <c r="I25" s="14">
-        <v>508</v>
+        <v>555</v>
       </c>
       <c r="J25" s="14">
-        <v>839</v>
+        <v>870</v>
       </c>
       <c r="K25" s="15">
-        <v>-39.451728247914</v>
+        <v>-36.206896551724</v>
       </c>
       <c r="L25" s="15">
-        <v>-32.981530343007</v>
+        <v>-30.100755667506</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
         <v>-66.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G26" s="14">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H26" s="15">
-        <v>26.315789473684</v>
+        <v>-23.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="J26" s="14">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K26" s="15">
-        <v>13.414634146341</v>
+        <v>4.255319148936</v>
       </c>
       <c r="L26" s="15">
-        <v>-7</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="M26" s="15">
-        <v>-7.920792079207</v>
+        <v>-9.259259259259</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,23 +1387,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
         <v>6</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>3</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
         <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
         <v>21</v>
       </c>
       <c r="J28" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K28" s="15">
-        <v>-8.695652173913</v>
+        <v>-16</v>
       </c>
       <c r="L28" s="15">
-        <v>-47.5</v>
+        <v>-51.162790697674</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-019pct.xlsx
+++ b/data/source/weekly/cs-en-us-019pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,7 +905,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -914,22 +914,22 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L15" s="15">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M15" s="15">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N15" s="15">
-        <v>20</v>
+        <v>14.285714285714</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F16" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G16" s="14">
         <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J16" s="14">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K16" s="15">
-        <v>-33.333333333333</v>
+        <v>-32.258064516129</v>
       </c>
       <c r="L16" s="15">
-        <v>-37.704918032786</v>
+        <v>-34.375</v>
       </c>
       <c r="M16" s="15">
-        <v>-9.523809523809</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.343963553530</v>
+        <v>-91.120507399577</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G17" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H17" s="15">
-        <v>-11.764705882352</v>
+        <v>-20</v>
       </c>
       <c r="I17" s="14">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="J17" s="14">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K17" s="15">
-        <v>6.779661016949</v>
+        <v>3.076923076923</v>
       </c>
       <c r="L17" s="15">
-        <v>34.042553191489</v>
+        <v>24.074074074074</v>
       </c>
       <c r="M17" s="15">
-        <v>117.241379310345</v>
+        <v>116.129032258065</v>
       </c>
       <c r="N17" s="15">
-        <v>-30</v>
+        <v>-28.723404255319</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
+        <v>2</v>
+      </c>
+      <c r="E18" s="15">
+        <v>150</v>
+      </c>
+      <c r="F18" s="14">
         <v>15</v>
       </c>
-      <c r="E18" s="15">
-        <v>-93.333333333333</v>
-      </c>
-      <c r="F18" s="14">
-        <v>16</v>
-      </c>
       <c r="G18" s="14">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H18" s="15">
-        <v>-52.941176470588</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I18" s="14">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="J18" s="14">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K18" s="15">
-        <v>-46.153846153846</v>
+        <v>-42.452830188679</v>
       </c>
       <c r="L18" s="15">
-        <v>-27.272727272727</v>
+        <v>-25.609756097561</v>
       </c>
       <c r="M18" s="15">
-        <v>-39.784946236559</v>
+        <v>-35.789473684210</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.614595210946</v>
+        <v>-93.419633225458</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,54 +1060,54 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D19" s="14">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E19" s="15">
-        <v>-5.882352941176</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="F19" s="14">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="G19" s="14">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="H19" s="15">
-        <v>-19.402985074626</v>
+        <v>-21.232876712328</v>
       </c>
       <c r="I19" s="14">
-        <v>445</v>
+        <v>472</v>
       </c>
       <c r="J19" s="14">
-        <v>483</v>
+        <v>522</v>
       </c>
       <c r="K19" s="15">
-        <v>-7.867494824016</v>
+        <v>-9.578544061302</v>
       </c>
       <c r="L19" s="15">
-        <v>-7.098121085594</v>
+        <v>-6.719367588932</v>
       </c>
       <c r="M19" s="15">
-        <v>16.187989556135</v>
+        <v>14.563106796116</v>
       </c>
       <c r="N19" s="15">
-        <v>-62.636439966414</v>
+        <v>-62.746645619573</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="14">
+      <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
@@ -1119,22 +1119,22 @@
         <v>-33.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J20" s="14">
         <v>15</v>
       </c>
       <c r="K20" s="15">
-        <v>6.666666666666</v>
+        <v>13.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-15.789473684210</v>
+        <v>-15</v>
       </c>
       <c r="M20" s="15">
-        <v>-15.789473684210</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="N20" s="15">
-        <v>-98.584070796460</v>
+        <v>-98.591549295774</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,48 +1142,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D21" s="17">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E21" s="18">
-        <v>-31.147540983606</v>
+        <v>-17.307692307692</v>
       </c>
       <c r="F21" s="17">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="G21" s="17">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="H21" s="18">
-        <v>-23.645320197044</v>
+        <v>-20.853080568720</v>
       </c>
       <c r="I21" s="17">
-        <v>625</v>
+        <v>668</v>
       </c>
       <c r="J21" s="17">
-        <v>722</v>
+        <v>774</v>
       </c>
       <c r="K21" s="18">
-        <v>-13.434903047091</v>
+        <v>-13.695090439276</v>
       </c>
       <c r="L21" s="18">
-        <v>-9.288824383164</v>
+        <v>-8.743169398907</v>
       </c>
       <c r="M21" s="18">
-        <v>9.457092819614</v>
+        <v>9.688013136289</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.266398929049</v>
+        <v>-83.207642031171</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>2</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1201,19 +1201,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J22" s="14">
         <v>11</v>
       </c>
       <c r="K22" s="15">
-        <v>27.272727272727</v>
+        <v>45.454545454545</v>
       </c>
       <c r="L22" s="15">
-        <v>7.692307692307</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M22" s="15">
-        <v>100</v>
+        <v>77.777777777777</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,38 +1223,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="C23" s="14">
+        <v>1</v>
+      </c>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J23" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K23" s="15">
-        <v>-53.846153846153</v>
+        <v>-50</v>
       </c>
       <c r="L23" s="15">
-        <v>-25</v>
+        <v>-12.5</v>
       </c>
       <c r="M23" s="15">
-        <v>-40</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D24" s="14">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="E24" s="15">
-        <v>76.666666666666</v>
+        <v>-4.255319148936</v>
       </c>
       <c r="F24" s="14">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="G24" s="14">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="H24" s="15">
-        <v>-16.585365853658</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="I24" s="14">
-        <v>750</v>
+        <v>793</v>
       </c>
       <c r="J24" s="14">
-        <v>1012</v>
+        <v>1059</v>
       </c>
       <c r="K24" s="15">
-        <v>-25.889328063241</v>
+        <v>-25.118035882908</v>
       </c>
       <c r="L24" s="15">
-        <v>-17.218543046357</v>
+        <v>-17.136886102403</v>
       </c>
       <c r="M24" s="15">
-        <v>55.925155925155</v>
+        <v>53.980582524271</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D25" s="14">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="E25" s="15">
-        <v>54.838709677419</v>
+        <v>6.818181818181</v>
       </c>
       <c r="F25" s="14">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="G25" s="14">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H25" s="15">
-        <v>-25.595238095238</v>
+        <v>-12.426035502958</v>
       </c>
       <c r="I25" s="14">
-        <v>555</v>
+        <v>602</v>
       </c>
       <c r="J25" s="14">
-        <v>870</v>
+        <v>914</v>
       </c>
       <c r="K25" s="15">
-        <v>-36.206896551724</v>
+        <v>-34.135667396061</v>
       </c>
       <c r="L25" s="15">
-        <v>-30.100755667506</v>
+        <v>-27.990430622009</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>-66.666666666666</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="F26" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G26" s="14">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H26" s="15">
-        <v>-23.333333333333</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="J26" s="14">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="K26" s="15">
-        <v>4.255319148936</v>
+        <v>-0.952380952380</v>
       </c>
       <c r="L26" s="15">
-        <v>-6.666666666666</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M26" s="15">
-        <v>-9.259259259259</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>2</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,25 +1397,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
         <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>-14.285714285714</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L27" s="15">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="14">
+      <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="I28" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J28" s="14">
         <v>25</v>
       </c>
       <c r="K28" s="15">
-        <v>-16</v>
+        <v>-4</v>
       </c>
       <c r="L28" s="15">
-        <v>-51.162790697674</v>
+        <v>-47.826086956521</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1554,32 +1554,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="14">
+      <c r="D31" s="14">
         <v>1</v>
       </c>
+      <c r="E31" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
+      </c>
       <c r="G31" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>
       </c>
       <c r="J31" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K31" s="15">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
       <c r="L31" s="15">
-        <v>-72.727272727272</v>
+        <v>-75</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-019pct.xlsx
+++ b/data/source/weekly/cs-en-us-019pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,7 +905,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-20</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G16" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I16" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J16" s="14">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K16" s="15">
-        <v>-32.258064516129</v>
+        <v>-29.6875</v>
       </c>
       <c r="L16" s="15">
-        <v>-34.375</v>
+        <v>-33.823529411764</v>
       </c>
       <c r="M16" s="15">
-        <v>-8.695652173913</v>
+        <v>-2.173913043478</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.120507399577</v>
+        <v>-90.890688259109</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,13 +978,13 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
         <v>16</v>
@@ -996,22 +996,22 @@
         <v>-20</v>
       </c>
       <c r="I17" s="14">
+        <v>70</v>
+      </c>
+      <c r="J17" s="14">
         <v>67</v>
       </c>
-      <c r="J17" s="14">
-        <v>65</v>
-      </c>
       <c r="K17" s="15">
-        <v>3.076923076923</v>
+        <v>4.477611940298</v>
       </c>
       <c r="L17" s="15">
-        <v>24.074074074074</v>
+        <v>14.754098360655</v>
       </c>
       <c r="M17" s="15">
-        <v>116.129032258065</v>
+        <v>118.75</v>
       </c>
       <c r="N17" s="15">
-        <v>-28.723404255319</v>
+        <v>-28.571428571428</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E18" s="15">
-        <v>150</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G18" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H18" s="15">
-        <v>-44.444444444444</v>
+        <v>-58.620689655172</v>
       </c>
       <c r="I18" s="14">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="J18" s="14">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="K18" s="15">
-        <v>-42.452830188679</v>
+        <v>-42.982456140350</v>
       </c>
       <c r="L18" s="15">
-        <v>-25.609756097561</v>
+        <v>-25.287356321839</v>
       </c>
       <c r="M18" s="15">
-        <v>-35.789473684210</v>
+        <v>-33.673469387755</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.419633225458</v>
+        <v>-93.298969072165</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D19" s="14">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E19" s="15">
-        <v>-30.769230769230</v>
+        <v>-25.806451612903</v>
       </c>
       <c r="F19" s="14">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G19" s="14">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H19" s="15">
-        <v>-21.232876712328</v>
+        <v>-22.147651006711</v>
       </c>
       <c r="I19" s="14">
-        <v>472</v>
+        <v>495</v>
       </c>
       <c r="J19" s="14">
-        <v>522</v>
+        <v>553</v>
       </c>
       <c r="K19" s="15">
-        <v>-9.578544061302</v>
+        <v>-10.488245931283</v>
       </c>
       <c r="L19" s="15">
-        <v>-6.719367588932</v>
+        <v>-6.779661016949</v>
       </c>
       <c r="M19" s="15">
-        <v>14.563106796116</v>
+        <v>13.013698630137</v>
       </c>
       <c r="N19" s="15">
-        <v>-62.746645619573</v>
+        <v>-63.004484304932</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D20" s="14">
+        <v>3</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="I20" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J20" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K20" s="15">
-        <v>13.333333333333</v>
+        <v>5.555555555555</v>
       </c>
       <c r="L20" s="15">
-        <v>-15</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="M20" s="15">
-        <v>-10.526315789473</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="N20" s="15">
-        <v>-98.591549295774</v>
+        <v>-98.492063492063</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D21" s="17">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E21" s="18">
-        <v>-17.307692307692</v>
+        <v>-23.913043478260</v>
       </c>
       <c r="F21" s="17">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G21" s="17">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="H21" s="18">
-        <v>-20.853080568720</v>
+        <v>-24.074074074074</v>
       </c>
       <c r="I21" s="17">
-        <v>668</v>
+        <v>703</v>
       </c>
       <c r="J21" s="17">
-        <v>774</v>
+        <v>820</v>
       </c>
       <c r="K21" s="18">
-        <v>-13.695090439276</v>
+        <v>-14.268292682926</v>
       </c>
       <c r="L21" s="18">
-        <v>-8.743169398907</v>
+        <v>-9.173126614987</v>
       </c>
       <c r="M21" s="18">
-        <v>9.688013136289</v>
+        <v>9.501557632398</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.207642031171</v>
+        <v>-83.141486810551</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,37 +1183,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>0</v>
       </c>
       <c r="F22" s="14">
         <v>4</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="G22" s="14">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15">
+        <v>300</v>
       </c>
       <c r="I22" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J22" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K22" s="15">
-        <v>45.454545454545</v>
+        <v>41.666666666666</v>
       </c>
       <c r="L22" s="15">
-        <v>14.285714285714</v>
+        <v>21.428571428571</v>
       </c>
       <c r="M22" s="15">
-        <v>77.777777777777</v>
+        <v>54.545454545454</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1226,35 +1226,35 @@
       <c r="C23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>0</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
         <v>2</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J23" s="14">
         <v>14</v>
       </c>
       <c r="K23" s="15">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L23" s="15">
-        <v>-12.5</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M23" s="15">
-        <v>-36.363636363636</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D24" s="14">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E24" s="15">
-        <v>-4.255319148936</v>
+        <v>20</v>
       </c>
       <c r="F24" s="14">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="G24" s="14">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="H24" s="15">
-        <v>-4.761904761904</v>
+        <v>15.384615384615</v>
       </c>
       <c r="I24" s="14">
-        <v>793</v>
+        <v>841</v>
       </c>
       <c r="J24" s="14">
-        <v>1059</v>
+        <v>1099</v>
       </c>
       <c r="K24" s="15">
-        <v>-25.118035882908</v>
+        <v>-23.475887170154</v>
       </c>
       <c r="L24" s="15">
-        <v>-17.136886102403</v>
+        <v>-16.484607745779</v>
       </c>
       <c r="M24" s="15">
-        <v>53.980582524271</v>
+        <v>51.805054151624</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D25" s="14">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="E25" s="15">
-        <v>6.818181818181</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="F25" s="14">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G25" s="14">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="H25" s="15">
-        <v>-12.426035502958</v>
+        <v>4.827586206896</v>
       </c>
       <c r="I25" s="14">
-        <v>602</v>
+        <v>627</v>
       </c>
       <c r="J25" s="14">
-        <v>914</v>
+        <v>943</v>
       </c>
       <c r="K25" s="15">
-        <v>-34.135667396061</v>
+        <v>-33.510074231177</v>
       </c>
       <c r="L25" s="15">
-        <v>-27.990430622009</v>
+        <v>-29.152542372881</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15">
-        <v>-45.454545454545</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F26" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G26" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H26" s="15">
-        <v>-41.666666666666</v>
+        <v>-41.025641025641</v>
       </c>
       <c r="I26" s="14">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="J26" s="14">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="K26" s="15">
-        <v>-0.952380952380</v>
+        <v>0.892857142857</v>
       </c>
       <c r="L26" s="15">
-        <v>-7.142857142857</v>
+        <v>-7.377049180327</v>
       </c>
       <c r="M26" s="15">
-        <v>-11.111111111111</v>
+        <v>-8.130081300813</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,7 +1388,7 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1406,16 +1406,16 @@
         <v>300</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" s="14">
         <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>14.285714285714</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L27" s="15">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="15">
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
         <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="I28" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J28" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K28" s="15">
-        <v>-4</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="L28" s="15">
-        <v>-47.826086956521</v>
+        <v>-46.808510638297</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1478,8 +1478,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1519,8 +1519,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1554,11 +1554,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
